--- a/transposon_tree/te_234_template2.xlsx
+++ b/transposon_tree/te_234_template2.xlsx
@@ -1,27 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fongi\Desktop\TE\transposon_tree\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F330CDE3-3CD7-46B1-80FE-8C67288E8B8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="1" xr2:uid="{CD76AF00-4E42-48FB-B369-ADDCAD91E3D0}"/>
+    <workbookView windowWidth="23040" windowHeight="10455" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="te_234_template2" sheetId="1" r:id="rId1"/>
     <sheet name="color" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="361">
   <si>
     <t>TE_Name</t>
   </si>
@@ -191,6 +198,9 @@
     <t>Family: DeuSINE</t>
   </si>
   <si>
+    <t>DNA transposons</t>
+  </si>
+  <si>
     <t>env</t>
   </si>
   <si>
@@ -239,6 +249,9 @@
     <t>exonized TE sequence</t>
   </si>
   <si>
+    <t>others</t>
+  </si>
+  <si>
     <t>FAM</t>
   </si>
   <si>
@@ -416,9 +429,6 @@
     <t>High copy number in HERV families</t>
   </si>
   <si>
-    <t>others</t>
-  </si>
-  <si>
     <t>highly truncated L1</t>
   </si>
   <si>
@@ -563,432 +573,441 @@
     <t>Family: SVA</t>
   </si>
   <si>
+    <t>Superfamily: SINE-R</t>
+  </si>
+  <si>
+    <t>LINE</t>
+  </si>
+  <si>
+    <t>LINE-1</t>
+  </si>
+  <si>
+    <t>LINE-1 analyte</t>
+  </si>
+  <si>
+    <t>LINE-1 families with different 5'UTR</t>
+  </si>
+  <si>
+    <t>LINE-1 promoter</t>
+  </si>
+  <si>
+    <t>LINE-1/Alu singleton</t>
+  </si>
+  <si>
+    <t>LINE-2</t>
+  </si>
+  <si>
+    <t>Looper</t>
+  </si>
+  <si>
+    <t>Superfamily: Unclassified TIR</t>
+  </si>
+  <si>
+    <t>LTR</t>
+  </si>
+  <si>
+    <t>LTR10</t>
+  </si>
+  <si>
+    <t>LTR10A</t>
+  </si>
+  <si>
+    <t>LTR10B</t>
+  </si>
+  <si>
+    <t>LTR12</t>
+  </si>
+  <si>
+    <t>LTR12C</t>
+  </si>
+  <si>
+    <t>LTR12D</t>
+  </si>
+  <si>
+    <t>LTR13</t>
+  </si>
+  <si>
+    <t>Family: HERVK13</t>
+  </si>
+  <si>
+    <t>LTR15</t>
+  </si>
+  <si>
+    <t>Family: Other ERV1 LTRs</t>
+  </si>
+  <si>
+    <t>LTR16B</t>
+  </si>
+  <si>
+    <t>LTR18A</t>
+  </si>
+  <si>
+    <t>LTR1A1</t>
+  </si>
+  <si>
+    <t>Family: LTR1-related</t>
+  </si>
+  <si>
+    <t>LTR2</t>
+  </si>
+  <si>
+    <t>LTR22</t>
+  </si>
+  <si>
+    <t>LTR3</t>
+  </si>
+  <si>
+    <t>Family: HERVK3</t>
+  </si>
+  <si>
+    <t>Family: LTR5</t>
+  </si>
+  <si>
+    <t>LTR5_Hs</t>
+  </si>
+  <si>
+    <t>LTR5A</t>
+  </si>
+  <si>
+    <t>LTR5B</t>
+  </si>
+  <si>
+    <t>LTR7</t>
+  </si>
+  <si>
+    <t>LTR70</t>
+  </si>
+  <si>
+    <t>LTR78</t>
+  </si>
+  <si>
+    <t>LTR7A</t>
+  </si>
+  <si>
+    <t>LTR7B</t>
+  </si>
+  <si>
+    <t>LTR7C</t>
+  </si>
+  <si>
+    <t>LTR7Y</t>
+  </si>
+  <si>
+    <t>LTR8B</t>
+  </si>
+  <si>
+    <t>Family: HUERS-P</t>
+  </si>
+  <si>
+    <t>Made1</t>
+  </si>
+  <si>
+    <t>Family: MADE1</t>
+  </si>
+  <si>
+    <t>MamRep434</t>
+  </si>
+  <si>
+    <t>Family: MamRep (Tc1)</t>
+  </si>
+  <si>
+    <t>MER1</t>
+  </si>
+  <si>
+    <t>Family: MER1</t>
+  </si>
+  <si>
+    <t>MER11</t>
+  </si>
+  <si>
+    <t>Family: HERVK11 (MER11)</t>
+  </si>
+  <si>
+    <t>MER117</t>
+  </si>
+  <si>
+    <t>Family: MER117</t>
+  </si>
+  <si>
+    <t>MER11A</t>
+  </si>
+  <si>
+    <t>MER11B</t>
+  </si>
+  <si>
+    <t>MER11C</t>
+  </si>
+  <si>
+    <t>MER130</t>
+  </si>
+  <si>
+    <t>Subclass VI: Unclassified DNA Transposons</t>
+  </si>
+  <si>
+    <t>MER131</t>
+  </si>
+  <si>
+    <t>Superfamily: Unclassified SINE</t>
+  </si>
+  <si>
+    <t>MER2</t>
+  </si>
+  <si>
+    <t>Family: MER2</t>
+  </si>
+  <si>
+    <t>MER20</t>
+  </si>
+  <si>
+    <t>Family: MER20</t>
+  </si>
+  <si>
+    <t>MER21C</t>
+  </si>
+  <si>
+    <t>Family: MER4-group</t>
+  </si>
+  <si>
+    <t>Family: MER21-group</t>
+  </si>
+  <si>
+    <t>MER39</t>
+  </si>
+  <si>
+    <t>MER41</t>
+  </si>
+  <si>
+    <t>Family: MER4I-group</t>
+  </si>
+  <si>
+    <t>MER44</t>
+  </si>
+  <si>
+    <t>Family: MER44</t>
+  </si>
+  <si>
+    <t>MER44B</t>
+  </si>
+  <si>
+    <t>MER46</t>
+  </si>
+  <si>
+    <t>Family: MER46</t>
+  </si>
+  <si>
+    <t>MER47</t>
+  </si>
+  <si>
+    <t>Family: MER47</t>
+  </si>
+  <si>
+    <t>MER48</t>
+  </si>
+  <si>
+    <t>MER49</t>
+  </si>
+  <si>
+    <t>MER5</t>
+  </si>
+  <si>
+    <t>Family: MER5</t>
+  </si>
+  <si>
+    <t>MER50</t>
+  </si>
+  <si>
+    <t>MER51</t>
+  </si>
+  <si>
+    <t>MER51A</t>
+  </si>
+  <si>
+    <t>MER51B</t>
+  </si>
+  <si>
+    <t>MER52A</t>
+  </si>
+  <si>
+    <t>MER53</t>
+  </si>
+  <si>
+    <t>MER57E3</t>
+  </si>
+  <si>
+    <t>MER6</t>
+  </si>
+  <si>
+    <t>Family: MER6</t>
+  </si>
+  <si>
+    <t>MER61</t>
+  </si>
+  <si>
+    <t>MER6A</t>
+  </si>
+  <si>
+    <t>MER75</t>
+  </si>
+  <si>
+    <t>Family: MER75</t>
+  </si>
+  <si>
+    <t>Superfamily: piggyBac</t>
+  </si>
+  <si>
+    <t>MER81</t>
+  </si>
+  <si>
+    <t>Family: MER81</t>
+  </si>
+  <si>
+    <t>MER85</t>
+  </si>
+  <si>
+    <t>MER9-LTR</t>
+  </si>
+  <si>
+    <t>Family: MER9</t>
+  </si>
+  <si>
+    <t>MER91B</t>
+  </si>
+  <si>
+    <t>Family: MER91</t>
+  </si>
+  <si>
+    <t>MER91C</t>
+  </si>
+  <si>
+    <t>MER96</t>
+  </si>
+  <si>
+    <t>Family: MER96</t>
+  </si>
+  <si>
+    <t>Merlin</t>
+  </si>
+  <si>
+    <t>Superfamily: Merlin</t>
+  </si>
+  <si>
+    <t>MIR</t>
+  </si>
+  <si>
+    <t>Family: MIR</t>
+  </si>
+  <si>
+    <t>Superfamily: SINE2/tRNA</t>
+  </si>
+  <si>
+    <t>MIR and AluSp</t>
+  </si>
+  <si>
+    <t>MIR and AluSp combination</t>
+  </si>
+  <si>
+    <t>MIR3</t>
+  </si>
+  <si>
+    <t>MIRb</t>
+  </si>
+  <si>
+    <t>MIRc</t>
+  </si>
+  <si>
+    <t>MLT1</t>
+  </si>
+  <si>
+    <t>Family: MaLR (Mammalian LTR Retrotransposons)</t>
+  </si>
+  <si>
+    <t>MLT1A</t>
+  </si>
+  <si>
+    <t>MLT1A1</t>
+  </si>
+  <si>
+    <t>MLT1F1</t>
+  </si>
+  <si>
+    <t>MLT1H</t>
+  </si>
+  <si>
+    <t>MLT2A1</t>
+  </si>
+  <si>
+    <t>Family: MLT2</t>
+  </si>
+  <si>
+    <t>MLT2A2</t>
+  </si>
+  <si>
+    <t>MLT2B3</t>
+  </si>
+  <si>
+    <t>Mobile element</t>
+  </si>
+  <si>
+    <t>MSTD</t>
+  </si>
+  <si>
+    <t>MstII</t>
+  </si>
+  <si>
+    <t>NR_SVA_381</t>
+  </si>
+  <si>
+    <t>older TE</t>
+  </si>
+  <si>
+    <t>Penelope</t>
+  </si>
+  <si>
+    <t>Superfamily: Penelope / Neptune</t>
+  </si>
+  <si>
+    <t>piggyBac</t>
+  </si>
+  <si>
+    <t>Polymorphic TE</t>
+  </si>
+  <si>
+    <t>Pre-existing retrotransposon</t>
+  </si>
+  <si>
+    <t>retroelement</t>
+  </si>
+  <si>
+    <t>retroposon</t>
+  </si>
+  <si>
+    <t>Retrotransposon</t>
+  </si>
+  <si>
+    <t>SINE</t>
+  </si>
+  <si>
+    <t>SINE (chr11:47608036-47608220)</t>
+  </si>
+  <si>
+    <t>SINE-R</t>
+  </si>
+  <si>
+    <t>SINE1/7SL</t>
+  </si>
+  <si>
+    <t>SINE3</t>
+  </si>
+  <si>
+    <t>SINE5</t>
+  </si>
+  <si>
+    <t>SVA</t>
+  </si>
+  <si>
     <t>Superfamily: SINE-R (SVA Family)</t>
   </si>
   <si>
-    <t>LINE</t>
-  </si>
-  <si>
-    <t>LINE-1</t>
-  </si>
-  <si>
-    <t>LINE-1 analyte</t>
-  </si>
-  <si>
-    <t>LINE-1 families with different 5'UTR</t>
-  </si>
-  <si>
-    <t>LINE-1 promoter</t>
-  </si>
-  <si>
-    <t>LINE-1/Alu singleton</t>
-  </si>
-  <si>
-    <t>LINE-2</t>
-  </si>
-  <si>
-    <t>Looper</t>
-  </si>
-  <si>
-    <t>Superfamily: Unclassified TIR</t>
-  </si>
-  <si>
-    <t>LTR</t>
-  </si>
-  <si>
-    <t>LTR10</t>
-  </si>
-  <si>
-    <t>LTR10A</t>
-  </si>
-  <si>
-    <t>LTR10B</t>
-  </si>
-  <si>
-    <t>LTR12</t>
-  </si>
-  <si>
-    <t>LTR12C</t>
-  </si>
-  <si>
-    <t>LTR12D</t>
-  </si>
-  <si>
-    <t>LTR13</t>
-  </si>
-  <si>
-    <t>Family: HERVK13</t>
-  </si>
-  <si>
-    <t>LTR15</t>
-  </si>
-  <si>
-    <t>Family: Other ERV1 LTRs</t>
-  </si>
-  <si>
-    <t>LTR16B</t>
-  </si>
-  <si>
-    <t>LTR18A</t>
-  </si>
-  <si>
-    <t>LTR1A1</t>
-  </si>
-  <si>
-    <t>Family: LTR1-related</t>
-  </si>
-  <si>
-    <t>LTR2</t>
-  </si>
-  <si>
-    <t>LTR22</t>
-  </si>
-  <si>
-    <t>LTR3</t>
-  </si>
-  <si>
-    <t>Family: HERVK3</t>
-  </si>
-  <si>
-    <t>Family: LTR5</t>
-  </si>
-  <si>
-    <t>LTR5_Hs</t>
-  </si>
-  <si>
-    <t>LTR5A</t>
-  </si>
-  <si>
-    <t>LTR5B</t>
-  </si>
-  <si>
-    <t>LTR7</t>
-  </si>
-  <si>
-    <t>LTR70</t>
-  </si>
-  <si>
-    <t>LTR78</t>
-  </si>
-  <si>
-    <t>LTR7A</t>
-  </si>
-  <si>
-    <t>LTR7B</t>
-  </si>
-  <si>
-    <t>LTR7C</t>
-  </si>
-  <si>
-    <t>LTR7Y</t>
-  </si>
-  <si>
-    <t>LTR8B</t>
-  </si>
-  <si>
-    <t>Family: HUERS-P</t>
-  </si>
-  <si>
-    <t>Made1</t>
-  </si>
-  <si>
-    <t>Family: MADE1</t>
-  </si>
-  <si>
-    <t>MamRep434</t>
-  </si>
-  <si>
-    <t>Family: MamRep (Tc1)</t>
-  </si>
-  <si>
-    <t>MER1</t>
-  </si>
-  <si>
-    <t>Family: MER1</t>
-  </si>
-  <si>
-    <t>MER11</t>
-  </si>
-  <si>
-    <t>Family: HERVK11 (MER11)</t>
-  </si>
-  <si>
-    <t>MER117</t>
-  </si>
-  <si>
-    <t>Family: MER117</t>
-  </si>
-  <si>
-    <t>MER11A</t>
-  </si>
-  <si>
-    <t>MER11B</t>
-  </si>
-  <si>
-    <t>MER11C</t>
-  </si>
-  <si>
-    <t>MER130</t>
-  </si>
-  <si>
-    <t>Subclass VI: Unclassified DNA Transposons</t>
-  </si>
-  <si>
-    <t>MER131</t>
-  </si>
-  <si>
-    <t>Superfamily: Unclassified SINE</t>
-  </si>
-  <si>
-    <t>MER2</t>
-  </si>
-  <si>
-    <t>Family: MER2</t>
-  </si>
-  <si>
-    <t>MER20</t>
-  </si>
-  <si>
-    <t>Family: MER20</t>
-  </si>
-  <si>
-    <t>MER21C</t>
-  </si>
-  <si>
-    <t>Family: MER4-group</t>
-  </si>
-  <si>
-    <t>Family: MER21-group</t>
-  </si>
-  <si>
-    <t>MER39</t>
-  </si>
-  <si>
-    <t>MER41</t>
-  </si>
-  <si>
-    <t>Family: MER4I-group</t>
-  </si>
-  <si>
-    <t>MER44</t>
-  </si>
-  <si>
-    <t>Family: MER44</t>
-  </si>
-  <si>
-    <t>MER44B</t>
-  </si>
-  <si>
-    <t>MER46</t>
-  </si>
-  <si>
-    <t>Family: MER46</t>
-  </si>
-  <si>
-    <t>MER47</t>
-  </si>
-  <si>
-    <t>Family: MER47</t>
-  </si>
-  <si>
-    <t>MER48</t>
-  </si>
-  <si>
-    <t>MER49</t>
-  </si>
-  <si>
-    <t>MER5</t>
-  </si>
-  <si>
-    <t>Family: MER5</t>
-  </si>
-  <si>
-    <t>MER50</t>
-  </si>
-  <si>
-    <t>MER51</t>
-  </si>
-  <si>
-    <t>MER51A</t>
-  </si>
-  <si>
-    <t>MER51B</t>
-  </si>
-  <si>
-    <t>MER52A</t>
-  </si>
-  <si>
-    <t>MER53</t>
-  </si>
-  <si>
-    <t>MER57E3</t>
-  </si>
-  <si>
-    <t>MER6</t>
-  </si>
-  <si>
-    <t>Family: MER6</t>
-  </si>
-  <si>
-    <t>MER61</t>
-  </si>
-  <si>
-    <t>MER6A</t>
-  </si>
-  <si>
-    <t>MER75</t>
-  </si>
-  <si>
-    <t>Family: MER75</t>
-  </si>
-  <si>
-    <t>Superfamily: piggyBac</t>
-  </si>
-  <si>
-    <t>MER81</t>
-  </si>
-  <si>
-    <t>Family: MER81</t>
-  </si>
-  <si>
-    <t>MER85</t>
-  </si>
-  <si>
-    <t>MER9-LTR</t>
-  </si>
-  <si>
-    <t>Family: MER9</t>
-  </si>
-  <si>
-    <t>MER91B</t>
-  </si>
-  <si>
-    <t>Family: MER91</t>
-  </si>
-  <si>
-    <t>MER91C</t>
-  </si>
-  <si>
-    <t>MER96</t>
-  </si>
-  <si>
-    <t>Family: MER96</t>
-  </si>
-  <si>
-    <t>Merlin</t>
-  </si>
-  <si>
-    <t>Superfamily: Merlin</t>
-  </si>
-  <si>
-    <t>MIR</t>
-  </si>
-  <si>
-    <t>Family: MIR</t>
-  </si>
-  <si>
-    <t>MIR and AluSp</t>
-  </si>
-  <si>
-    <t>MIR and AluSp combination</t>
-  </si>
-  <si>
-    <t>MIR3</t>
-  </si>
-  <si>
-    <t>MIRb</t>
-  </si>
-  <si>
-    <t>MIRc</t>
-  </si>
-  <si>
-    <t>MLT1</t>
-  </si>
-  <si>
-    <t>Family: MaLR (Mammalian LTR Retrotransposons)</t>
-  </si>
-  <si>
-    <t>MLT1A</t>
-  </si>
-  <si>
-    <t>MLT1A1</t>
-  </si>
-  <si>
-    <t>MLT1F1</t>
-  </si>
-  <si>
-    <t>MLT1H</t>
-  </si>
-  <si>
-    <t>MLT2A1</t>
-  </si>
-  <si>
-    <t>Family: MLT2</t>
-  </si>
-  <si>
-    <t>MLT2A2</t>
-  </si>
-  <si>
-    <t>MLT2B3</t>
-  </si>
-  <si>
-    <t>Mobile element</t>
-  </si>
-  <si>
-    <t>MSTD</t>
-  </si>
-  <si>
-    <t>MstII</t>
-  </si>
-  <si>
-    <t>NR_SVA_381</t>
-  </si>
-  <si>
-    <t>older TE</t>
-  </si>
-  <si>
-    <t>Penelope</t>
-  </si>
-  <si>
-    <t>Superfamily: Penelope / Neptune</t>
-  </si>
-  <si>
-    <t>piggyBac</t>
-  </si>
-  <si>
-    <t>Polymorphic TE</t>
-  </si>
-  <si>
-    <t>Pre-existing retrotransposon</t>
-  </si>
-  <si>
-    <t>retroelement</t>
-  </si>
-  <si>
-    <t>Retrotransposon</t>
-  </si>
-  <si>
-    <t>SINE</t>
-  </si>
-  <si>
-    <t>SINE (chr11:47608036-47608220)</t>
-  </si>
-  <si>
-    <t>SINE-R</t>
-  </si>
-  <si>
-    <t>SINE1/7SL</t>
-  </si>
-  <si>
-    <t>SINE3</t>
-  </si>
-  <si>
-    <t>SINE5</t>
-  </si>
-  <si>
-    <t>SVA</t>
-  </si>
-  <si>
     <t>SVA_A</t>
   </si>
   <si>
@@ -1028,6 +1047,9 @@
     <t>Tigger3a</t>
   </si>
   <si>
+    <t>Transposable element</t>
+  </si>
+  <si>
     <t>Transposon</t>
   </si>
   <si>
@@ -1040,115 +1062,86 @@
     <t>Other LINE-2/CR1 Elements</t>
   </si>
   <si>
-    <t>Superfamily: SINE-R</t>
-  </si>
-  <si>
-    <t>Superfamily: SINE-R</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>others</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Superfamily: SINE2/tRNA</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>DNA transposons</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Superfamily: SINE1/7SL (Alu Family)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>紫色</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>HERV-16对应树上HERV16</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>HERV-I对应HERVI</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>FLAM C对应FLAM_C</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>预防搅乱分类最好将转座子名字对应回树上</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>红色</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>重复</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>29、统一为DNA transposons</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>29、237、238统一为DNA transposons</t>
   </si>
   <si>
     <t>34、55、73统一为ERVL</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>85、112统一为LINE-1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>retroposon</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>215、216统一为retroposon</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Transposable element</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>237、238统一为Transposable element</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>黄色</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>因为不知道你要怎么实现，我姑且标注了黄的，黄色代表这个转座子不是父类的子类，就是父类，例如LINE-1就是Superfamily: L1(LINE-1)。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>绿色</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>看备注</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>此外发现若干大小写对不上树的问题，忘记标记了，不知道对你建树有没有影响</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1156,24 +1149,45 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="3"/>
       <name val="等线 Light"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1182,7 +1196,6 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1191,31 +1204,6 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1223,7 +1211,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1232,7 +1219,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1241,15 +1227,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1258,24 +1235,13 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1284,7 +1250,27 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1292,22 +1278,6 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1321,175 +1291,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -1500,13 +1303,193 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor rgb="FF7030A0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7030A0"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1517,6 +1500,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1542,7 +1540,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.399975585192419"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1577,15 +1575,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1601,17 +1590,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1627,56 +1610,68 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1685,73 +1680,82 @@
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1759,74 +1763,77 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="42">
-    <cellStyle name="20% - 着色 1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="标题" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="标题 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="标题 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="标题 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="标题 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="差" xfId="7" builtinId="27" customBuiltin="1"/>
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="汇总" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="计算" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="检查单元格" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="解释性文本" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="警告文本" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="链接单元格" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="适中" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="输出" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="输入" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="着色 1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="着色 2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="着色 3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="着色 4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="着色 5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="着色 6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="注释" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1875,7 +1882,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1908,26 +1915,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1960,23 +1950,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -2118,21 +2091,16 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6AD8287-2871-434B-9772-81957BDBC0A5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J240"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.65"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2164,12 +2132,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>344</v>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
@@ -2184,7 +2152,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -2207,7 +2175,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -2230,7 +2198,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -2253,7 +2221,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -2276,7 +2244,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -2299,7 +2267,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -2322,7 +2290,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -2345,7 +2313,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -2368,7 +2336,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -2391,7 +2359,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -2414,7 +2382,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -2437,7 +2405,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -2460,7 +2428,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -2483,7 +2451,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -2506,7 +2474,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -2529,7 +2497,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -2552,7 +2520,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
         <v>35</v>
       </c>
@@ -2575,7 +2543,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -2598,7 +2566,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
         <v>37</v>
       </c>
@@ -2621,7 +2589,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -2641,7 +2609,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -2658,7 +2626,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="24" spans="1:9">
       <c r="A24" t="s">
         <v>43</v>
       </c>
@@ -2681,7 +2649,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="25" spans="1:9">
       <c r="A25" t="s">
         <v>46</v>
       </c>
@@ -2704,11 +2672,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="26" spans="1:9">
       <c r="A26" t="s">
         <v>47</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C26" t="s">
@@ -2730,11 +2698,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="27" spans="1:9">
       <c r="A27" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C27" t="s">
@@ -2747,7 +2715,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="28" spans="1:9">
       <c r="A28" t="s">
         <v>54</v>
       </c>
@@ -2770,11 +2738,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.65">
-      <c r="A29" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="B29" s="3" t="s">
+    <row r="29" spans="1:9">
+      <c r="A29" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C29" t="s">
@@ -2784,24 +2752,24 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
@@ -2813,18 +2781,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="C31" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D31" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E31" t="s">
         <v>13</v>
@@ -2836,21 +2804,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>63</v>
-      </c>
-      <c r="B32" s="3" t="s">
         <v>64</v>
       </c>
+      <c r="B32" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="C32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D32" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E32" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F32" t="s">
         <v>13</v>
@@ -2862,21 +2830,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>65</v>
-      </c>
-      <c r="B33" s="3" t="s">
         <v>66</v>
       </c>
+      <c r="B33" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="C33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F33" t="s">
         <v>13</v>
@@ -2888,27 +2856,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A34" s="1" t="s">
+    <row r="34" spans="1:10">
+      <c r="A34" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34" t="s">
         <v>67</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C34" t="s">
-        <v>69</v>
-      </c>
-      <c r="D34" t="s">
-        <v>66</v>
-      </c>
       <c r="E34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H34" t="s">
         <v>13</v>
@@ -2920,24 +2888,24 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
+        <v>71</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="C35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D35" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G35" t="s">
         <v>13</v>
@@ -2949,12 +2917,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B36" t="s">
-        <v>341</v>
+        <v>73</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
@@ -2963,12 +2931,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C37" t="s">
         <v>11</v>
@@ -2986,12 +2954,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A38" s="5" t="s">
-        <v>74</v>
+    <row r="38" spans="1:10">
+      <c r="A38" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="B38" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C38" t="s">
         <v>11</v>
@@ -3009,12 +2977,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
+        <v>77</v>
+      </c>
+      <c r="B39" t="s">
         <v>75</v>
-      </c>
-      <c r="B39" t="s">
-        <v>73</v>
       </c>
       <c r="C39" t="s">
         <v>11</v>
@@ -3032,15 +3000,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B40" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C40" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D40" t="s">
         <v>41</v>
@@ -3055,18 +3023,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>79</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="C41" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E41" t="s">
         <v>13</v>
@@ -3078,12 +3046,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B42" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C42" t="s">
         <v>50</v>
@@ -3101,21 +3069,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D43" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F43" t="s">
         <v>13</v>
@@ -3127,11 +3095,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>86</v>
-      </c>
-      <c r="B44" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C44" t="s">
@@ -3147,12 +3115,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>87</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="C45" t="s">
         <v>45</v>
@@ -3170,12 +3138,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>89</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="C46" t="s">
         <v>42</v>
@@ -3187,15 +3155,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>91</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>60</v>
+        <v>93</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="C47" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D47" t="s">
         <v>13</v>
@@ -3207,789 +3175,789 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A48" s="5" t="s">
-        <v>92</v>
+    <row r="48" spans="1:10">
+      <c r="A48" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="B48" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C48" t="s">
+        <v>70</v>
+      </c>
+      <c r="D48" t="s">
+        <v>67</v>
+      </c>
+      <c r="E48" t="s">
+        <v>60</v>
+      </c>
+      <c r="F48" t="s">
+        <v>61</v>
+      </c>
+      <c r="G48" t="s">
+        <v>62</v>
+      </c>
+      <c r="H48" t="s">
+        <v>13</v>
+      </c>
+      <c r="I48" t="s">
+        <v>14</v>
+      </c>
+      <c r="J48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" t="s">
+        <v>95</v>
+      </c>
+      <c r="B49" t="s">
+        <v>96</v>
+      </c>
+      <c r="C49" t="s">
+        <v>60</v>
+      </c>
+      <c r="D49" t="s">
+        <v>61</v>
+      </c>
+      <c r="E49" t="s">
+        <v>62</v>
+      </c>
+      <c r="F49" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" t="s">
+        <v>14</v>
+      </c>
+      <c r="H49" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C50" t="s">
+        <v>60</v>
+      </c>
+      <c r="D50" t="s">
+        <v>61</v>
+      </c>
+      <c r="E50" t="s">
+        <v>62</v>
+      </c>
+      <c r="F50" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" t="s">
+        <v>14</v>
+      </c>
+      <c r="H50" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" t="s">
+        <v>99</v>
+      </c>
+      <c r="B51" t="s">
+        <v>100</v>
+      </c>
+      <c r="C51" t="s">
+        <v>101</v>
+      </c>
+      <c r="D51" t="s">
+        <v>65</v>
+      </c>
+      <c r="E51" t="s">
+        <v>60</v>
+      </c>
+      <c r="F51" t="s">
+        <v>61</v>
+      </c>
+      <c r="G51" t="s">
+        <v>62</v>
+      </c>
+      <c r="H51" t="s">
+        <v>13</v>
+      </c>
+      <c r="I51" t="s">
+        <v>14</v>
+      </c>
+      <c r="J51" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" t="s">
+        <v>102</v>
+      </c>
+      <c r="B52" t="s">
+        <v>103</v>
+      </c>
+      <c r="C52" t="s">
+        <v>65</v>
+      </c>
+      <c r="D52" t="s">
+        <v>60</v>
+      </c>
+      <c r="E52" t="s">
+        <v>61</v>
+      </c>
+      <c r="F52" t="s">
+        <v>62</v>
+      </c>
+      <c r="G52" t="s">
+        <v>13</v>
+      </c>
+      <c r="H52" t="s">
+        <v>14</v>
+      </c>
+      <c r="I52" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" t="s">
+        <v>104</v>
+      </c>
+      <c r="B53" t="s">
+        <v>103</v>
+      </c>
+      <c r="C53" t="s">
+        <v>65</v>
+      </c>
+      <c r="D53" t="s">
+        <v>60</v>
+      </c>
+      <c r="E53" t="s">
+        <v>61</v>
+      </c>
+      <c r="F53" t="s">
+        <v>62</v>
+      </c>
+      <c r="G53" t="s">
+        <v>13</v>
+      </c>
+      <c r="H53" t="s">
+        <v>14</v>
+      </c>
+      <c r="I53" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" t="s">
+        <v>105</v>
+      </c>
+      <c r="B54" t="s">
+        <v>103</v>
+      </c>
+      <c r="C54" t="s">
+        <v>65</v>
+      </c>
+      <c r="D54" t="s">
+        <v>60</v>
+      </c>
+      <c r="E54" t="s">
+        <v>61</v>
+      </c>
+      <c r="F54" t="s">
+        <v>62</v>
+      </c>
+      <c r="G54" t="s">
+        <v>13</v>
+      </c>
+      <c r="H54" t="s">
+        <v>14</v>
+      </c>
+      <c r="I54" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D48" t="s">
-        <v>66</v>
-      </c>
-      <c r="E48" t="s">
+      <c r="C55" t="s">
+        <v>70</v>
+      </c>
+      <c r="D55" t="s">
+        <v>67</v>
+      </c>
+      <c r="E55" t="s">
+        <v>60</v>
+      </c>
+      <c r="F55" t="s">
+        <v>61</v>
+      </c>
+      <c r="G55" t="s">
+        <v>62</v>
+      </c>
+      <c r="H55" t="s">
+        <v>13</v>
+      </c>
+      <c r="I55" t="s">
+        <v>14</v>
+      </c>
+      <c r="J55" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" t="s">
+        <v>107</v>
+      </c>
+      <c r="B56" t="s">
+        <v>108</v>
+      </c>
+      <c r="C56" t="s">
+        <v>60</v>
+      </c>
+      <c r="D56" t="s">
+        <v>61</v>
+      </c>
+      <c r="E56" t="s">
+        <v>62</v>
+      </c>
+      <c r="F56" t="s">
+        <v>13</v>
+      </c>
+      <c r="G56" t="s">
+        <v>14</v>
+      </c>
+      <c r="H56" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" t="s">
+        <v>109</v>
+      </c>
+      <c r="B57" t="s">
+        <v>69</v>
+      </c>
+      <c r="C57" t="s">
+        <v>70</v>
+      </c>
+      <c r="D57" t="s">
+        <v>67</v>
+      </c>
+      <c r="E57" t="s">
+        <v>60</v>
+      </c>
+      <c r="F57" t="s">
+        <v>61</v>
+      </c>
+      <c r="G57" t="s">
+        <v>62</v>
+      </c>
+      <c r="H57" t="s">
+        <v>13</v>
+      </c>
+      <c r="I57" t="s">
+        <v>14</v>
+      </c>
+      <c r="J57" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" t="s">
+        <v>110</v>
+      </c>
+      <c r="B58" t="s">
+        <v>111</v>
+      </c>
+      <c r="C58" t="s">
+        <v>60</v>
+      </c>
+      <c r="D58" t="s">
+        <v>61</v>
+      </c>
+      <c r="E58" t="s">
+        <v>62</v>
+      </c>
+      <c r="F58" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58" t="s">
+        <v>14</v>
+      </c>
+      <c r="H58" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" t="s">
+        <v>112</v>
+      </c>
+      <c r="B59" t="s">
+        <v>111</v>
+      </c>
+      <c r="C59" t="s">
+        <v>60</v>
+      </c>
+      <c r="D59" t="s">
+        <v>61</v>
+      </c>
+      <c r="E59" t="s">
+        <v>62</v>
+      </c>
+      <c r="F59" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" t="s">
+        <v>14</v>
+      </c>
+      <c r="H59" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" t="s">
+        <v>113</v>
+      </c>
+      <c r="B60" t="s">
+        <v>114</v>
+      </c>
+      <c r="C60" t="s">
+        <v>60</v>
+      </c>
+      <c r="D60" t="s">
+        <v>61</v>
+      </c>
+      <c r="E60" t="s">
+        <v>62</v>
+      </c>
+      <c r="F60" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60" t="s">
+        <v>14</v>
+      </c>
+      <c r="H60" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" t="s">
+        <v>115</v>
+      </c>
+      <c r="B61" t="s">
+        <v>114</v>
+      </c>
+      <c r="C61" t="s">
+        <v>60</v>
+      </c>
+      <c r="D61" t="s">
+        <v>61</v>
+      </c>
+      <c r="E61" t="s">
+        <v>62</v>
+      </c>
+      <c r="F61" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" t="s">
+        <v>14</v>
+      </c>
+      <c r="H61" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" t="s">
+        <v>116</v>
+      </c>
+      <c r="B62" t="s">
+        <v>114</v>
+      </c>
+      <c r="C62" t="s">
+        <v>60</v>
+      </c>
+      <c r="D62" t="s">
+        <v>61</v>
+      </c>
+      <c r="E62" t="s">
+        <v>62</v>
+      </c>
+      <c r="F62" t="s">
+        <v>13</v>
+      </c>
+      <c r="G62" t="s">
+        <v>14</v>
+      </c>
+      <c r="H62" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" t="s">
+        <v>117</v>
+      </c>
+      <c r="B63" t="s">
+        <v>87</v>
+      </c>
+      <c r="C63" t="s">
+        <v>60</v>
+      </c>
+      <c r="D63" t="s">
+        <v>61</v>
+      </c>
+      <c r="E63" t="s">
+        <v>62</v>
+      </c>
+      <c r="F63" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" t="s">
+        <v>14</v>
+      </c>
+      <c r="H63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" t="s">
+        <v>118</v>
+      </c>
+      <c r="B64" t="s">
+        <v>87</v>
+      </c>
+      <c r="C64" t="s">
+        <v>60</v>
+      </c>
+      <c r="D64" t="s">
+        <v>61</v>
+      </c>
+      <c r="E64" t="s">
+        <v>62</v>
+      </c>
+      <c r="F64" t="s">
+        <v>13</v>
+      </c>
+      <c r="G64" t="s">
+        <v>14</v>
+      </c>
+      <c r="H64" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" t="s">
+        <v>119</v>
+      </c>
+      <c r="B65" t="s">
+        <v>120</v>
+      </c>
+      <c r="C65" t="s">
+        <v>60</v>
+      </c>
+      <c r="D65" t="s">
+        <v>61</v>
+      </c>
+      <c r="E65" t="s">
+        <v>62</v>
+      </c>
+      <c r="F65" t="s">
+        <v>13</v>
+      </c>
+      <c r="G65" t="s">
+        <v>14</v>
+      </c>
+      <c r="H65" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" t="s">
+        <v>121</v>
+      </c>
+      <c r="B66" t="s">
+        <v>98</v>
+      </c>
+      <c r="C66" t="s">
+        <v>60</v>
+      </c>
+      <c r="D66" t="s">
+        <v>61</v>
+      </c>
+      <c r="E66" t="s">
+        <v>62</v>
+      </c>
+      <c r="F66" t="s">
+        <v>13</v>
+      </c>
+      <c r="G66" t="s">
+        <v>14</v>
+      </c>
+      <c r="H66" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" t="s">
+        <v>122</v>
+      </c>
+      <c r="B67" t="s">
+        <v>103</v>
+      </c>
+      <c r="C67" t="s">
+        <v>65</v>
+      </c>
+      <c r="D67" t="s">
+        <v>60</v>
+      </c>
+      <c r="E67" t="s">
+        <v>61</v>
+      </c>
+      <c r="F67" t="s">
+        <v>62</v>
+      </c>
+      <c r="G67" t="s">
+        <v>13</v>
+      </c>
+      <c r="H67" t="s">
+        <v>14</v>
+      </c>
+      <c r="I67" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" t="s">
+        <v>123</v>
+      </c>
+      <c r="B68" t="s">
+        <v>103</v>
+      </c>
+      <c r="C68" t="s">
+        <v>65</v>
+      </c>
+      <c r="D68" t="s">
+        <v>60</v>
+      </c>
+      <c r="E68" t="s">
+        <v>61</v>
+      </c>
+      <c r="F68" t="s">
+        <v>62</v>
+      </c>
+      <c r="G68" t="s">
+        <v>13</v>
+      </c>
+      <c r="H68" t="s">
+        <v>14</v>
+      </c>
+      <c r="I68" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" t="s">
+        <v>124</v>
+      </c>
+      <c r="B69" t="s">
+        <v>103</v>
+      </c>
+      <c r="C69" t="s">
+        <v>65</v>
+      </c>
+      <c r="D69" t="s">
+        <v>60</v>
+      </c>
+      <c r="E69" t="s">
+        <v>61</v>
+      </c>
+      <c r="F69" t="s">
+        <v>62</v>
+      </c>
+      <c r="G69" t="s">
+        <v>13</v>
+      </c>
+      <c r="H69" t="s">
+        <v>14</v>
+      </c>
+      <c r="I69" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" t="s">
+        <v>125</v>
+      </c>
+      <c r="B70" t="s">
+        <v>126</v>
+      </c>
+      <c r="C70" t="s">
+        <v>65</v>
+      </c>
+      <c r="D70" t="s">
+        <v>60</v>
+      </c>
+      <c r="E70" t="s">
+        <v>61</v>
+      </c>
+      <c r="F70" t="s">
+        <v>62</v>
+      </c>
+      <c r="G70" t="s">
+        <v>13</v>
+      </c>
+      <c r="H70" t="s">
+        <v>14</v>
+      </c>
+      <c r="I70" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" t="s">
+        <v>127</v>
+      </c>
+      <c r="B71" t="s">
+        <v>103</v>
+      </c>
+      <c r="C71" t="s">
+        <v>65</v>
+      </c>
+      <c r="D71" t="s">
+        <v>60</v>
+      </c>
+      <c r="E71" t="s">
+        <v>61</v>
+      </c>
+      <c r="F71" t="s">
+        <v>62</v>
+      </c>
+      <c r="G71" t="s">
+        <v>13</v>
+      </c>
+      <c r="H71" t="s">
+        <v>14</v>
+      </c>
+      <c r="I71" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" t="s">
+        <v>128</v>
+      </c>
+      <c r="B72" t="s">
+        <v>103</v>
+      </c>
+      <c r="C72" t="s">
+        <v>65</v>
+      </c>
+      <c r="D72" t="s">
+        <v>60</v>
+      </c>
+      <c r="E72" t="s">
+        <v>61</v>
+      </c>
+      <c r="F72" t="s">
+        <v>62</v>
+      </c>
+      <c r="G72" t="s">
+        <v>13</v>
+      </c>
+      <c r="H72" t="s">
+        <v>14</v>
+      </c>
+      <c r="I72" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C73" t="s">
+        <v>70</v>
+      </c>
+      <c r="D73" t="s">
+        <v>67</v>
+      </c>
+      <c r="E73" t="s">
+        <v>60</v>
+      </c>
+      <c r="F73" t="s">
+        <v>61</v>
+      </c>
+      <c r="G73" t="s">
+        <v>62</v>
+      </c>
+      <c r="H73" t="s">
+        <v>13</v>
+      </c>
+      <c r="I73" t="s">
+        <v>14</v>
+      </c>
+      <c r="J73" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" t="s">
+        <v>130</v>
+      </c>
+      <c r="B74" t="s">
+        <v>69</v>
+      </c>
+      <c r="C74" t="s">
+        <v>70</v>
+      </c>
+      <c r="D74" t="s">
+        <v>67</v>
+      </c>
+      <c r="E74" t="s">
+        <v>60</v>
+      </c>
+      <c r="F74" t="s">
+        <v>61</v>
+      </c>
+      <c r="G74" t="s">
+        <v>62</v>
+      </c>
+      <c r="H74" t="s">
+        <v>13</v>
+      </c>
+      <c r="I74" t="s">
+        <v>14</v>
+      </c>
+      <c r="J74" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" t="s">
+        <v>131</v>
+      </c>
+      <c r="B75" t="s">
+        <v>58</v>
+      </c>
+      <c r="C75" t="s">
         <v>59</v>
       </c>
-      <c r="F48" t="s">
-        <v>60</v>
-      </c>
-      <c r="G48" t="s">
-        <v>61</v>
-      </c>
-      <c r="H48" t="s">
-        <v>13</v>
-      </c>
-      <c r="I48" t="s">
-        <v>14</v>
-      </c>
-      <c r="J48" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A49" t="s">
-        <v>93</v>
-      </c>
-      <c r="B49" t="s">
-        <v>94</v>
-      </c>
-      <c r="C49" t="s">
-        <v>59</v>
-      </c>
-      <c r="D49" t="s">
-        <v>60</v>
-      </c>
-      <c r="E49" t="s">
-        <v>61</v>
-      </c>
-      <c r="F49" t="s">
-        <v>13</v>
-      </c>
-      <c r="G49" t="s">
-        <v>14</v>
-      </c>
-      <c r="H49" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A50" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C50" t="s">
-        <v>59</v>
-      </c>
-      <c r="D50" t="s">
-        <v>60</v>
-      </c>
-      <c r="E50" t="s">
-        <v>61</v>
-      </c>
-      <c r="F50" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" t="s">
-        <v>14</v>
-      </c>
-      <c r="H50" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A51" t="s">
-        <v>97</v>
-      </c>
-      <c r="B51" t="s">
-        <v>98</v>
-      </c>
-      <c r="C51" t="s">
-        <v>99</v>
-      </c>
-      <c r="D51" t="s">
-        <v>64</v>
-      </c>
-      <c r="E51" t="s">
-        <v>59</v>
-      </c>
-      <c r="F51" t="s">
-        <v>60</v>
-      </c>
-      <c r="G51" t="s">
-        <v>61</v>
-      </c>
-      <c r="H51" t="s">
-        <v>13</v>
-      </c>
-      <c r="I51" t="s">
-        <v>14</v>
-      </c>
-      <c r="J51" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A52" t="s">
-        <v>100</v>
-      </c>
-      <c r="B52" t="s">
-        <v>101</v>
-      </c>
-      <c r="C52" t="s">
-        <v>64</v>
-      </c>
-      <c r="D52" t="s">
-        <v>59</v>
-      </c>
-      <c r="E52" t="s">
-        <v>60</v>
-      </c>
-      <c r="F52" t="s">
-        <v>61</v>
-      </c>
-      <c r="G52" t="s">
-        <v>13</v>
-      </c>
-      <c r="H52" t="s">
-        <v>14</v>
-      </c>
-      <c r="I52" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A53" t="s">
-        <v>102</v>
-      </c>
-      <c r="B53" t="s">
-        <v>101</v>
-      </c>
-      <c r="C53" t="s">
-        <v>64</v>
-      </c>
-      <c r="D53" t="s">
-        <v>59</v>
-      </c>
-      <c r="E53" t="s">
-        <v>60</v>
-      </c>
-      <c r="F53" t="s">
-        <v>61</v>
-      </c>
-      <c r="G53" t="s">
-        <v>13</v>
-      </c>
-      <c r="H53" t="s">
-        <v>14</v>
-      </c>
-      <c r="I53" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B54" t="s">
-        <v>101</v>
-      </c>
-      <c r="C54" t="s">
-        <v>64</v>
-      </c>
-      <c r="D54" t="s">
-        <v>59</v>
-      </c>
-      <c r="E54" t="s">
-        <v>60</v>
-      </c>
-      <c r="F54" t="s">
-        <v>61</v>
-      </c>
-      <c r="G54" t="s">
-        <v>13</v>
-      </c>
-      <c r="H54" t="s">
-        <v>14</v>
-      </c>
-      <c r="I54" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A55" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C55" t="s">
-        <v>69</v>
-      </c>
-      <c r="D55" t="s">
-        <v>66</v>
-      </c>
-      <c r="E55" t="s">
-        <v>59</v>
-      </c>
-      <c r="F55" t="s">
-        <v>60</v>
-      </c>
-      <c r="G55" t="s">
-        <v>61</v>
-      </c>
-      <c r="H55" t="s">
-        <v>13</v>
-      </c>
-      <c r="I55" t="s">
-        <v>14</v>
-      </c>
-      <c r="J55" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A56" t="s">
-        <v>105</v>
-      </c>
-      <c r="B56" t="s">
-        <v>106</v>
-      </c>
-      <c r="C56" t="s">
-        <v>59</v>
-      </c>
-      <c r="D56" t="s">
-        <v>60</v>
-      </c>
-      <c r="E56" t="s">
-        <v>61</v>
-      </c>
-      <c r="F56" t="s">
-        <v>13</v>
-      </c>
-      <c r="G56" t="s">
-        <v>14</v>
-      </c>
-      <c r="H56" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A57" t="s">
-        <v>107</v>
-      </c>
-      <c r="B57" t="s">
-        <v>68</v>
-      </c>
-      <c r="C57" t="s">
-        <v>69</v>
-      </c>
-      <c r="D57" t="s">
-        <v>66</v>
-      </c>
-      <c r="E57" t="s">
-        <v>59</v>
-      </c>
-      <c r="F57" t="s">
-        <v>60</v>
-      </c>
-      <c r="G57" t="s">
-        <v>61</v>
-      </c>
-      <c r="H57" t="s">
-        <v>13</v>
-      </c>
-      <c r="I57" t="s">
-        <v>14</v>
-      </c>
-      <c r="J57" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A58" t="s">
-        <v>108</v>
-      </c>
-      <c r="B58" t="s">
-        <v>109</v>
-      </c>
-      <c r="C58" t="s">
-        <v>59</v>
-      </c>
-      <c r="D58" t="s">
-        <v>60</v>
-      </c>
-      <c r="E58" t="s">
-        <v>61</v>
-      </c>
-      <c r="F58" t="s">
-        <v>13</v>
-      </c>
-      <c r="G58" t="s">
-        <v>14</v>
-      </c>
-      <c r="H58" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A59" t="s">
-        <v>110</v>
-      </c>
-      <c r="B59" t="s">
-        <v>109</v>
-      </c>
-      <c r="C59" t="s">
-        <v>59</v>
-      </c>
-      <c r="D59" t="s">
-        <v>60</v>
-      </c>
-      <c r="E59" t="s">
-        <v>61</v>
-      </c>
-      <c r="F59" t="s">
-        <v>13</v>
-      </c>
-      <c r="G59" t="s">
-        <v>14</v>
-      </c>
-      <c r="H59" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A60" t="s">
-        <v>111</v>
-      </c>
-      <c r="B60" t="s">
-        <v>112</v>
-      </c>
-      <c r="C60" t="s">
-        <v>59</v>
-      </c>
-      <c r="D60" t="s">
-        <v>60</v>
-      </c>
-      <c r="E60" t="s">
-        <v>61</v>
-      </c>
-      <c r="F60" t="s">
-        <v>13</v>
-      </c>
-      <c r="G60" t="s">
-        <v>14</v>
-      </c>
-      <c r="H60" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A61" t="s">
-        <v>113</v>
-      </c>
-      <c r="B61" t="s">
-        <v>112</v>
-      </c>
-      <c r="C61" t="s">
-        <v>59</v>
-      </c>
-      <c r="D61" t="s">
-        <v>60</v>
-      </c>
-      <c r="E61" t="s">
-        <v>61</v>
-      </c>
-      <c r="F61" t="s">
-        <v>13</v>
-      </c>
-      <c r="G61" t="s">
-        <v>14</v>
-      </c>
-      <c r="H61" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A62" t="s">
-        <v>114</v>
-      </c>
-      <c r="B62" t="s">
-        <v>112</v>
-      </c>
-      <c r="C62" t="s">
-        <v>59</v>
-      </c>
-      <c r="D62" t="s">
-        <v>60</v>
-      </c>
-      <c r="E62" t="s">
-        <v>61</v>
-      </c>
-      <c r="F62" t="s">
-        <v>13</v>
-      </c>
-      <c r="G62" t="s">
-        <v>14</v>
-      </c>
-      <c r="H62" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A63" t="s">
-        <v>115</v>
-      </c>
-      <c r="B63" t="s">
-        <v>85</v>
-      </c>
-      <c r="C63" t="s">
-        <v>59</v>
-      </c>
-      <c r="D63" t="s">
-        <v>60</v>
-      </c>
-      <c r="E63" t="s">
-        <v>61</v>
-      </c>
-      <c r="F63" t="s">
-        <v>13</v>
-      </c>
-      <c r="G63" t="s">
-        <v>14</v>
-      </c>
-      <c r="H63" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A64" t="s">
-        <v>116</v>
-      </c>
-      <c r="B64" t="s">
-        <v>85</v>
-      </c>
-      <c r="C64" t="s">
-        <v>59</v>
-      </c>
-      <c r="D64" t="s">
-        <v>60</v>
-      </c>
-      <c r="E64" t="s">
-        <v>61</v>
-      </c>
-      <c r="F64" t="s">
-        <v>13</v>
-      </c>
-      <c r="G64" t="s">
-        <v>14</v>
-      </c>
-      <c r="H64" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A65" t="s">
-        <v>117</v>
-      </c>
-      <c r="B65" t="s">
-        <v>118</v>
-      </c>
-      <c r="C65" t="s">
-        <v>59</v>
-      </c>
-      <c r="D65" t="s">
-        <v>60</v>
-      </c>
-      <c r="E65" t="s">
-        <v>61</v>
-      </c>
-      <c r="F65" t="s">
-        <v>13</v>
-      </c>
-      <c r="G65" t="s">
-        <v>14</v>
-      </c>
-      <c r="H65" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A66" t="s">
-        <v>119</v>
-      </c>
-      <c r="B66" t="s">
-        <v>96</v>
-      </c>
-      <c r="C66" t="s">
-        <v>59</v>
-      </c>
-      <c r="D66" t="s">
-        <v>60</v>
-      </c>
-      <c r="E66" t="s">
-        <v>61</v>
-      </c>
-      <c r="F66" t="s">
-        <v>13</v>
-      </c>
-      <c r="G66" t="s">
-        <v>14</v>
-      </c>
-      <c r="H66" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A67" t="s">
-        <v>120</v>
-      </c>
-      <c r="B67" t="s">
-        <v>101</v>
-      </c>
-      <c r="C67" t="s">
-        <v>64</v>
-      </c>
-      <c r="D67" t="s">
-        <v>59</v>
-      </c>
-      <c r="E67" t="s">
-        <v>60</v>
-      </c>
-      <c r="F67" t="s">
-        <v>61</v>
-      </c>
-      <c r="G67" t="s">
-        <v>13</v>
-      </c>
-      <c r="H67" t="s">
-        <v>14</v>
-      </c>
-      <c r="I67" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A68" t="s">
-        <v>121</v>
-      </c>
-      <c r="B68" t="s">
-        <v>101</v>
-      </c>
-      <c r="C68" t="s">
-        <v>64</v>
-      </c>
-      <c r="D68" t="s">
-        <v>59</v>
-      </c>
-      <c r="E68" t="s">
-        <v>60</v>
-      </c>
-      <c r="F68" t="s">
-        <v>61</v>
-      </c>
-      <c r="G68" t="s">
-        <v>13</v>
-      </c>
-      <c r="H68" t="s">
-        <v>14</v>
-      </c>
-      <c r="I68" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A69" t="s">
-        <v>122</v>
-      </c>
-      <c r="B69" t="s">
-        <v>101</v>
-      </c>
-      <c r="C69" t="s">
-        <v>64</v>
-      </c>
-      <c r="D69" t="s">
-        <v>59</v>
-      </c>
-      <c r="E69" t="s">
-        <v>60</v>
-      </c>
-      <c r="F69" t="s">
-        <v>61</v>
-      </c>
-      <c r="G69" t="s">
-        <v>13</v>
-      </c>
-      <c r="H69" t="s">
-        <v>14</v>
-      </c>
-      <c r="I69" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A70" t="s">
-        <v>123</v>
-      </c>
-      <c r="B70" t="s">
-        <v>124</v>
-      </c>
-      <c r="C70" t="s">
-        <v>64</v>
-      </c>
-      <c r="D70" t="s">
-        <v>59</v>
-      </c>
-      <c r="E70" t="s">
-        <v>60</v>
-      </c>
-      <c r="F70" t="s">
-        <v>61</v>
-      </c>
-      <c r="G70" t="s">
-        <v>13</v>
-      </c>
-      <c r="H70" t="s">
-        <v>14</v>
-      </c>
-      <c r="I70" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A71" t="s">
-        <v>125</v>
-      </c>
-      <c r="B71" t="s">
-        <v>101</v>
-      </c>
-      <c r="C71" t="s">
-        <v>64</v>
-      </c>
-      <c r="D71" t="s">
-        <v>59</v>
-      </c>
-      <c r="E71" t="s">
-        <v>60</v>
-      </c>
-      <c r="F71" t="s">
-        <v>61</v>
-      </c>
-      <c r="G71" t="s">
-        <v>13</v>
-      </c>
-      <c r="H71" t="s">
-        <v>14</v>
-      </c>
-      <c r="I71" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A72" t="s">
-        <v>126</v>
-      </c>
-      <c r="B72" t="s">
-        <v>101</v>
-      </c>
-      <c r="C72" t="s">
-        <v>64</v>
-      </c>
-      <c r="D72" t="s">
-        <v>59</v>
-      </c>
-      <c r="E72" t="s">
-        <v>60</v>
-      </c>
-      <c r="F72" t="s">
-        <v>61</v>
-      </c>
-      <c r="G72" t="s">
-        <v>13</v>
-      </c>
-      <c r="H72" t="s">
-        <v>14</v>
-      </c>
-      <c r="I72" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A73" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C73" t="s">
-        <v>69</v>
-      </c>
-      <c r="D73" t="s">
-        <v>66</v>
-      </c>
-      <c r="E73" t="s">
-        <v>59</v>
-      </c>
-      <c r="F73" t="s">
-        <v>60</v>
-      </c>
-      <c r="G73" t="s">
-        <v>61</v>
-      </c>
-      <c r="H73" t="s">
-        <v>13</v>
-      </c>
-      <c r="I73" t="s">
-        <v>14</v>
-      </c>
-      <c r="J73" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A74" t="s">
-        <v>128</v>
-      </c>
-      <c r="B74" t="s">
-        <v>68</v>
-      </c>
-      <c r="C74" t="s">
-        <v>69</v>
-      </c>
-      <c r="D74" t="s">
-        <v>66</v>
-      </c>
-      <c r="E74" t="s">
-        <v>59</v>
-      </c>
-      <c r="F74" t="s">
-        <v>60</v>
-      </c>
-      <c r="G74" t="s">
-        <v>61</v>
-      </c>
-      <c r="H74" t="s">
-        <v>13</v>
-      </c>
-      <c r="I74" t="s">
-        <v>14</v>
-      </c>
-      <c r="J74" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A75" t="s">
-        <v>129</v>
-      </c>
-      <c r="B75" t="s">
-        <v>57</v>
-      </c>
-      <c r="C75" t="s">
-        <v>58</v>
-      </c>
       <c r="D75" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E75" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F75" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G75" t="s">
         <v>13</v>
@@ -4001,12 +3969,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="76" spans="1:10">
       <c r="A76" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B76" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
@@ -4015,12 +3983,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="77" spans="1:10">
       <c r="A77" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B77" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="C77" t="s">
         <v>14</v>
@@ -4029,23 +3997,23 @@
         <v>15</v>
       </c>
     </row>
-    <row r="78" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.65">
-      <c r="A78" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B78" s="4" t="s">
+    <row r="78" s="1" customFormat="1" spans="1:10">
+      <c r="A78" s="1" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.65">
+      <c r="B78" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
       <c r="A79" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B79" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C79" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D79" t="s">
         <v>41</v>
@@ -4060,15 +4028,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="80" spans="1:10">
       <c r="A80" t="s">
+        <v>138</v>
+      </c>
+      <c r="B80" t="s">
         <v>137</v>
       </c>
-      <c r="B80" t="s">
-        <v>136</v>
-      </c>
       <c r="C80" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D80" t="s">
         <v>41</v>
@@ -4083,24 +4051,24 @@
         <v>15</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="81" spans="1:9">
       <c r="A81" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B81" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C81" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D81" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E81" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F81" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G81" t="s">
         <v>13</v>
@@ -4112,12 +4080,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="82" spans="1:9">
       <c r="A82" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B82" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="C82" t="s">
         <v>14</v>
@@ -4126,9 +4094,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="83" spans="1:9">
       <c r="A83" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B83" t="s">
         <v>11</v>
@@ -4146,12 +4114,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="84" spans="1:9">
       <c r="A84" t="s">
-        <v>141</v>
-      </c>
-      <c r="B84" s="3" t="s">
         <v>142</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>143</v>
       </c>
       <c r="C84" t="s">
         <v>42</v>
@@ -4163,11 +4131,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.65">
-      <c r="A85" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B85" s="3" t="s">
+    <row r="85" spans="1:9">
+      <c r="A85" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B85" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C85" t="s">
@@ -4183,12 +4151,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="86" spans="1:9">
       <c r="A86" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B86" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C86" t="s">
         <v>50</v>
@@ -4206,12 +4174,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="87" spans="1:9">
       <c r="A87" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B87" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C87" t="s">
         <v>50</v>
@@ -4229,12 +4197,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="88" spans="1:9">
       <c r="A88" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B88" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C88" t="s">
         <v>50</v>
@@ -4252,12 +4220,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="89" spans="1:9">
       <c r="A89" t="s">
-        <v>149</v>
-      </c>
-      <c r="B89" s="3" t="s">
         <v>150</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>151</v>
       </c>
       <c r="C89" t="s">
         <v>50</v>
@@ -4275,12 +4243,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="90" spans="1:9">
       <c r="A90" t="s">
+        <v>152</v>
+      </c>
+      <c r="B90" t="s">
         <v>151</v>
-      </c>
-      <c r="B90" t="s">
-        <v>150</v>
       </c>
       <c r="C90" t="s">
         <v>50</v>
@@ -4298,12 +4266,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="91" spans="1:9">
       <c r="A91" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B91" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C91" t="s">
         <v>50</v>
@@ -4321,12 +4289,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="92" spans="1:9">
       <c r="A92" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B92" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C92" t="s">
         <v>50</v>
@@ -4344,12 +4312,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="93" spans="1:9">
       <c r="A93" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B93" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C93" t="s">
         <v>50</v>
@@ -4367,12 +4335,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="94" spans="1:9">
       <c r="A94" t="s">
+        <v>158</v>
+      </c>
+      <c r="B94" t="s">
         <v>157</v>
-      </c>
-      <c r="B94" t="s">
-        <v>156</v>
       </c>
       <c r="C94" t="s">
         <v>50</v>
@@ -4390,20 +4358,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="95" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.65">
-      <c r="A95" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B95" s="4" t="s">
+    <row r="95" s="1" customFormat="1" spans="1:9">
+      <c r="A95" s="1" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.65">
+      <c r="B95" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
       <c r="A96" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B96" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C96" t="s">
         <v>50</v>
@@ -4421,12 +4389,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.65">
+    <row r="97" spans="1:8">
       <c r="A97" t="s">
-        <v>162</v>
-      </c>
-      <c r="B97" s="3" t="s">
         <v>163</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>164</v>
       </c>
       <c r="C97" t="s">
         <v>50</v>
@@ -4444,12 +4412,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.65">
+    <row r="98" spans="1:8">
       <c r="A98" t="s">
+        <v>165</v>
+      </c>
+      <c r="B98" t="s">
         <v>164</v>
-      </c>
-      <c r="B98" t="s">
-        <v>163</v>
       </c>
       <c r="C98" t="s">
         <v>50</v>
@@ -4467,12 +4435,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.65">
+    <row r="99" spans="1:8">
       <c r="A99" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B99" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C99" t="s">
         <v>50</v>
@@ -4490,12 +4458,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.65">
+    <row r="100" spans="1:8">
       <c r="A100" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B100" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C100" t="s">
         <v>50</v>
@@ -4513,12 +4481,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.65">
+    <row r="101" spans="1:8">
       <c r="A101" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B101" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C101" t="s">
         <v>50</v>
@@ -4536,12 +4504,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.65">
+    <row r="102" spans="1:8">
       <c r="A102" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B102" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C102" t="s">
         <v>50</v>
@@ -4559,12 +4527,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.65">
+    <row r="103" spans="1:8">
       <c r="A103" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B103" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C103" t="s">
         <v>50</v>
@@ -4582,12 +4550,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.65">
+    <row r="104" spans="1:8">
       <c r="A104" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B104" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C104" t="s">
         <v>50</v>
@@ -4605,12 +4573,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.65">
+    <row r="105" spans="1:8">
       <c r="A105" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B105" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C105" t="s">
         <v>50</v>
@@ -4628,12 +4596,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.65">
+    <row r="106" spans="1:8">
       <c r="A106" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B106" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C106" t="s">
         <v>50</v>
@@ -4651,12 +4619,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.65">
+    <row r="107" spans="1:8">
       <c r="A107" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B107" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="C107" t="s">
         <v>14</v>
@@ -4665,12 +4633,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.65">
+    <row r="108" spans="1:8">
       <c r="A108" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B108" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C108" t="s">
         <v>49</v>
@@ -4688,12 +4656,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.65">
+    <row r="109" spans="1:8">
       <c r="A109" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B109" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C109" t="s">
         <v>49</v>
@@ -4714,15 +4682,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.65">
+    <row r="110" spans="1:8">
       <c r="A110" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B110" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C110" t="s">
-        <v>340</v>
+        <v>181</v>
       </c>
       <c r="D110" t="s">
         <v>12</v>
@@ -4737,11 +4705,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.65">
+    <row r="111" spans="1:8">
       <c r="A111" t="s">
-        <v>181</v>
-      </c>
-      <c r="B111" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B111" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C111" t="s">
@@ -4754,11 +4722,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.65">
-      <c r="A112" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B112" s="3" t="s">
+    <row r="112" spans="1:8">
+      <c r="A112" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B112" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C112" t="s">
@@ -4774,12 +4742,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="113" spans="1:10">
       <c r="A113" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B113" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="C113" t="s">
         <v>14</v>
@@ -4788,12 +4756,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="114" spans="1:10">
       <c r="A114" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B114" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="C114" t="s">
         <v>14</v>
@@ -4802,12 +4770,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="115" spans="1:10">
       <c r="A115" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B115" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="C115" t="s">
         <v>14</v>
@@ -4816,12 +4784,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="116" spans="1:10">
       <c r="A116" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B116" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="C116" t="s">
         <v>14</v>
@@ -4830,12 +4798,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="117" spans="1:10">
       <c r="A117" t="s">
-        <v>187</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>175</v>
+        <v>188</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>176</v>
       </c>
       <c r="C117" t="s">
         <v>49</v>
@@ -4856,12 +4824,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="118" spans="1:10">
       <c r="A118" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B118" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C118" t="s">
         <v>41</v>
@@ -4876,12 +4844,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="119" spans="1:10">
       <c r="A119" t="s">
-        <v>190</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>61</v>
+        <v>191</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="C119" t="s">
         <v>13</v>
@@ -4893,21 +4861,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="120" spans="1:10">
       <c r="A120" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B120" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C120" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D120" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E120" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F120" t="s">
         <v>13</v>
@@ -4919,21 +4887,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="121" spans="1:10">
       <c r="A121" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B121" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C121" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D121" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E121" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F121" t="s">
         <v>13</v>
@@ -4945,21 +4913,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="122" spans="1:10">
       <c r="A122" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B122" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C122" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D122" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E122" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F122" t="s">
         <v>13</v>
@@ -4971,21 +4939,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="123" spans="1:10">
       <c r="A123" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B123" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C123" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D123" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E123" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F123" t="s">
         <v>13</v>
@@ -4997,21 +4965,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="124" spans="1:10">
       <c r="A124" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B124" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C124" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D124" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E124" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F124" t="s">
         <v>13</v>
@@ -5023,21 +4991,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="125" spans="1:10">
       <c r="A125" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B125" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C125" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D125" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E125" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F125" t="s">
         <v>13</v>
@@ -5049,24 +5017,24 @@
         <v>15</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="126" spans="1:10">
       <c r="A126" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B126" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C126" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D126" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E126" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F126" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G126" t="s">
         <v>13</v>
@@ -5078,21 +5046,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="127" spans="1:10">
       <c r="A127" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B127" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C127" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D127" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E127" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F127" t="s">
         <v>13</v>
@@ -5104,595 +5072,595 @@
         <v>15</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="128" spans="1:10">
       <c r="A128" t="s">
+        <v>202</v>
+      </c>
+      <c r="B128" t="s">
+        <v>69</v>
+      </c>
+      <c r="C128" t="s">
+        <v>70</v>
+      </c>
+      <c r="D128" t="s">
+        <v>67</v>
+      </c>
+      <c r="E128" t="s">
+        <v>60</v>
+      </c>
+      <c r="F128" t="s">
+        <v>61</v>
+      </c>
+      <c r="G128" t="s">
+        <v>62</v>
+      </c>
+      <c r="H128" t="s">
+        <v>13</v>
+      </c>
+      <c r="I128" t="s">
+        <v>14</v>
+      </c>
+      <c r="J128" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10">
+      <c r="A129" t="s">
+        <v>203</v>
+      </c>
+      <c r="B129" t="s">
+        <v>69</v>
+      </c>
+      <c r="C129" t="s">
+        <v>70</v>
+      </c>
+      <c r="D129" t="s">
+        <v>67</v>
+      </c>
+      <c r="E129" t="s">
+        <v>60</v>
+      </c>
+      <c r="F129" t="s">
+        <v>61</v>
+      </c>
+      <c r="G129" t="s">
+        <v>62</v>
+      </c>
+      <c r="H129" t="s">
+        <v>13</v>
+      </c>
+      <c r="I129" t="s">
+        <v>14</v>
+      </c>
+      <c r="J129" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10">
+      <c r="A130" t="s">
+        <v>204</v>
+      </c>
+      <c r="B130" t="s">
+        <v>205</v>
+      </c>
+      <c r="C130" t="s">
+        <v>60</v>
+      </c>
+      <c r="D130" t="s">
+        <v>61</v>
+      </c>
+      <c r="E130" t="s">
+        <v>62</v>
+      </c>
+      <c r="F130" t="s">
+        <v>13</v>
+      </c>
+      <c r="G130" t="s">
+        <v>14</v>
+      </c>
+      <c r="H130" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10">
+      <c r="A131" t="s">
+        <v>206</v>
+      </c>
+      <c r="B131" t="s">
+        <v>87</v>
+      </c>
+      <c r="C131" t="s">
+        <v>60</v>
+      </c>
+      <c r="D131" t="s">
+        <v>61</v>
+      </c>
+      <c r="E131" t="s">
+        <v>62</v>
+      </c>
+      <c r="F131" t="s">
+        <v>13</v>
+      </c>
+      <c r="G131" t="s">
+        <v>14</v>
+      </c>
+      <c r="H131" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10">
+      <c r="A132" t="s">
+        <v>207</v>
+      </c>
+      <c r="B132" t="s">
+        <v>126</v>
+      </c>
+      <c r="C132" t="s">
+        <v>65</v>
+      </c>
+      <c r="D132" t="s">
+        <v>60</v>
+      </c>
+      <c r="E132" t="s">
+        <v>61</v>
+      </c>
+      <c r="F132" t="s">
+        <v>62</v>
+      </c>
+      <c r="G132" t="s">
+        <v>13</v>
+      </c>
+      <c r="H132" t="s">
+        <v>14</v>
+      </c>
+      <c r="I132" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10">
+      <c r="A133" t="s">
+        <v>208</v>
+      </c>
+      <c r="B133" t="s">
+        <v>209</v>
+      </c>
+      <c r="C133" t="s">
+        <v>65</v>
+      </c>
+      <c r="D133" t="s">
+        <v>60</v>
+      </c>
+      <c r="E133" t="s">
+        <v>61</v>
+      </c>
+      <c r="F133" t="s">
+        <v>62</v>
+      </c>
+      <c r="G133" t="s">
+        <v>13</v>
+      </c>
+      <c r="H133" t="s">
+        <v>14</v>
+      </c>
+      <c r="I133" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10">
+      <c r="A134" t="s">
+        <v>101</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C134" t="s">
+        <v>65</v>
+      </c>
+      <c r="D134" t="s">
+        <v>60</v>
+      </c>
+      <c r="E134" t="s">
+        <v>61</v>
+      </c>
+      <c r="F134" t="s">
+        <v>62</v>
+      </c>
+      <c r="G134" t="s">
+        <v>13</v>
+      </c>
+      <c r="H134" t="s">
+        <v>14</v>
+      </c>
+      <c r="I134" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10">
+      <c r="A135" t="s">
+        <v>211</v>
+      </c>
+      <c r="B135" t="s">
+        <v>210</v>
+      </c>
+      <c r="C135" t="s">
+        <v>65</v>
+      </c>
+      <c r="D135" t="s">
+        <v>60</v>
+      </c>
+      <c r="E135" t="s">
+        <v>61</v>
+      </c>
+      <c r="F135" t="s">
+        <v>62</v>
+      </c>
+      <c r="G135" t="s">
+        <v>13</v>
+      </c>
+      <c r="H135" t="s">
+        <v>14</v>
+      </c>
+      <c r="I135" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10">
+      <c r="A136" t="s">
+        <v>212</v>
+      </c>
+      <c r="B136" t="s">
+        <v>210</v>
+      </c>
+      <c r="C136" t="s">
+        <v>65</v>
+      </c>
+      <c r="D136" t="s">
+        <v>60</v>
+      </c>
+      <c r="E136" t="s">
+        <v>61</v>
+      </c>
+      <c r="F136" t="s">
+        <v>62</v>
+      </c>
+      <c r="G136" t="s">
+        <v>13</v>
+      </c>
+      <c r="H136" t="s">
+        <v>14</v>
+      </c>
+      <c r="I136" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10">
+      <c r="A137" t="s">
+        <v>213</v>
+      </c>
+      <c r="B137" t="s">
+        <v>210</v>
+      </c>
+      <c r="C137" t="s">
+        <v>65</v>
+      </c>
+      <c r="D137" t="s">
+        <v>60</v>
+      </c>
+      <c r="E137" t="s">
+        <v>61</v>
+      </c>
+      <c r="F137" t="s">
+        <v>62</v>
+      </c>
+      <c r="G137" t="s">
+        <v>13</v>
+      </c>
+      <c r="H137" t="s">
+        <v>14</v>
+      </c>
+      <c r="I137" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10">
+      <c r="A138" t="s">
+        <v>214</v>
+      </c>
+      <c r="B138" t="s">
         <v>201</v>
       </c>
-      <c r="B128" t="s">
-        <v>68</v>
-      </c>
-      <c r="C128" t="s">
+      <c r="C138" t="s">
+        <v>60</v>
+      </c>
+      <c r="D138" t="s">
+        <v>61</v>
+      </c>
+      <c r="E138" t="s">
+        <v>62</v>
+      </c>
+      <c r="F138" t="s">
+        <v>13</v>
+      </c>
+      <c r="G138" t="s">
+        <v>14</v>
+      </c>
+      <c r="H138" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10">
+      <c r="A139" t="s">
+        <v>215</v>
+      </c>
+      <c r="B139" t="s">
+        <v>201</v>
+      </c>
+      <c r="C139" t="s">
+        <v>60</v>
+      </c>
+      <c r="D139" t="s">
+        <v>61</v>
+      </c>
+      <c r="E139" t="s">
+        <v>62</v>
+      </c>
+      <c r="F139" t="s">
+        <v>13</v>
+      </c>
+      <c r="G139" t="s">
+        <v>14</v>
+      </c>
+      <c r="H139" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10">
+      <c r="A140" t="s">
+        <v>216</v>
+      </c>
+      <c r="B140" t="s">
+        <v>201</v>
+      </c>
+      <c r="C140" t="s">
+        <v>60</v>
+      </c>
+      <c r="D140" t="s">
+        <v>61</v>
+      </c>
+      <c r="E140" t="s">
+        <v>62</v>
+      </c>
+      <c r="F140" t="s">
+        <v>13</v>
+      </c>
+      <c r="G140" t="s">
+        <v>14</v>
+      </c>
+      <c r="H140" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10">
+      <c r="A141" t="s">
+        <v>217</v>
+      </c>
+      <c r="B141" t="s">
+        <v>120</v>
+      </c>
+      <c r="C141" t="s">
+        <v>60</v>
+      </c>
+      <c r="D141" t="s">
+        <v>61</v>
+      </c>
+      <c r="E141" t="s">
+        <v>62</v>
+      </c>
+      <c r="F141" t="s">
+        <v>13</v>
+      </c>
+      <c r="G141" t="s">
+        <v>14</v>
+      </c>
+      <c r="H141" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10">
+      <c r="A142" t="s">
+        <v>217</v>
+      </c>
+      <c r="B142" t="s">
         <v>69</v>
       </c>
-      <c r="D128" t="s">
-        <v>66</v>
-      </c>
-      <c r="E128" t="s">
-        <v>59</v>
-      </c>
-      <c r="F128" t="s">
-        <v>60</v>
-      </c>
-      <c r="G128" t="s">
-        <v>61</v>
-      </c>
-      <c r="H128" t="s">
-        <v>13</v>
-      </c>
-      <c r="I128" t="s">
-        <v>14</v>
-      </c>
-      <c r="J128" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A129" t="s">
-        <v>202</v>
-      </c>
-      <c r="B129" t="s">
-        <v>68</v>
-      </c>
-      <c r="C129" t="s">
+      <c r="C142" t="s">
+        <v>70</v>
+      </c>
+      <c r="D142" t="s">
+        <v>67</v>
+      </c>
+      <c r="E142" t="s">
+        <v>60</v>
+      </c>
+      <c r="F142" t="s">
+        <v>61</v>
+      </c>
+      <c r="G142" t="s">
+        <v>62</v>
+      </c>
+      <c r="H142" t="s">
+        <v>13</v>
+      </c>
+      <c r="I142" t="s">
+        <v>14</v>
+      </c>
+      <c r="J142" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10">
+      <c r="A143" t="s">
+        <v>218</v>
+      </c>
+      <c r="B143" t="s">
+        <v>120</v>
+      </c>
+      <c r="C143" t="s">
+        <v>60</v>
+      </c>
+      <c r="D143" t="s">
+        <v>61</v>
+      </c>
+      <c r="E143" t="s">
+        <v>62</v>
+      </c>
+      <c r="F143" t="s">
+        <v>13</v>
+      </c>
+      <c r="G143" t="s">
+        <v>14</v>
+      </c>
+      <c r="H143" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10">
+      <c r="A144" t="s">
+        <v>218</v>
+      </c>
+      <c r="B144" t="s">
         <v>69</v>
       </c>
-      <c r="D129" t="s">
-        <v>66</v>
-      </c>
-      <c r="E129" t="s">
-        <v>59</v>
-      </c>
-      <c r="F129" t="s">
-        <v>60</v>
-      </c>
-      <c r="G129" t="s">
-        <v>61</v>
-      </c>
-      <c r="H129" t="s">
-        <v>13</v>
-      </c>
-      <c r="I129" t="s">
-        <v>14</v>
-      </c>
-      <c r="J129" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A130" t="s">
-        <v>203</v>
-      </c>
-      <c r="B130" t="s">
-        <v>204</v>
-      </c>
-      <c r="C130" t="s">
-        <v>59</v>
-      </c>
-      <c r="D130" t="s">
-        <v>60</v>
-      </c>
-      <c r="E130" t="s">
-        <v>61</v>
-      </c>
-      <c r="F130" t="s">
-        <v>13</v>
-      </c>
-      <c r="G130" t="s">
-        <v>14</v>
-      </c>
-      <c r="H130" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A131" t="s">
-        <v>205</v>
-      </c>
-      <c r="B131" t="s">
-        <v>85</v>
-      </c>
-      <c r="C131" t="s">
-        <v>59</v>
-      </c>
-      <c r="D131" t="s">
-        <v>60</v>
-      </c>
-      <c r="E131" t="s">
-        <v>61</v>
-      </c>
-      <c r="F131" t="s">
-        <v>13</v>
-      </c>
-      <c r="G131" t="s">
-        <v>14</v>
-      </c>
-      <c r="H131" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A132" t="s">
-        <v>206</v>
-      </c>
-      <c r="B132" t="s">
-        <v>124</v>
-      </c>
-      <c r="C132" t="s">
-        <v>64</v>
-      </c>
-      <c r="D132" t="s">
-        <v>59</v>
-      </c>
-      <c r="E132" t="s">
-        <v>60</v>
-      </c>
-      <c r="F132" t="s">
-        <v>61</v>
-      </c>
-      <c r="G132" t="s">
-        <v>13</v>
-      </c>
-      <c r="H132" t="s">
-        <v>14</v>
-      </c>
-      <c r="I132" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A133" t="s">
-        <v>207</v>
-      </c>
-      <c r="B133" t="s">
-        <v>208</v>
-      </c>
-      <c r="C133" t="s">
-        <v>64</v>
-      </c>
-      <c r="D133" t="s">
-        <v>59</v>
-      </c>
-      <c r="E133" t="s">
-        <v>60</v>
-      </c>
-      <c r="F133" t="s">
-        <v>61</v>
-      </c>
-      <c r="G133" t="s">
-        <v>13</v>
-      </c>
-      <c r="H133" t="s">
-        <v>14</v>
-      </c>
-      <c r="I133" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A134" t="s">
-        <v>99</v>
-      </c>
-      <c r="B134" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C134" t="s">
-        <v>64</v>
-      </c>
-      <c r="D134" t="s">
-        <v>59</v>
-      </c>
-      <c r="E134" t="s">
-        <v>60</v>
-      </c>
-      <c r="F134" t="s">
-        <v>61</v>
-      </c>
-      <c r="G134" t="s">
-        <v>13</v>
-      </c>
-      <c r="H134" t="s">
-        <v>14</v>
-      </c>
-      <c r="I134" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A135" t="s">
-        <v>210</v>
-      </c>
-      <c r="B135" t="s">
-        <v>209</v>
-      </c>
-      <c r="C135" t="s">
-        <v>64</v>
-      </c>
-      <c r="D135" t="s">
-        <v>59</v>
-      </c>
-      <c r="E135" t="s">
-        <v>60</v>
-      </c>
-      <c r="F135" t="s">
-        <v>61</v>
-      </c>
-      <c r="G135" t="s">
-        <v>13</v>
-      </c>
-      <c r="H135" t="s">
-        <v>14</v>
-      </c>
-      <c r="I135" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A136" t="s">
-        <v>211</v>
-      </c>
-      <c r="B136" t="s">
-        <v>209</v>
-      </c>
-      <c r="C136" t="s">
-        <v>64</v>
-      </c>
-      <c r="D136" t="s">
-        <v>59</v>
-      </c>
-      <c r="E136" t="s">
-        <v>60</v>
-      </c>
-      <c r="F136" t="s">
-        <v>61</v>
-      </c>
-      <c r="G136" t="s">
-        <v>13</v>
-      </c>
-      <c r="H136" t="s">
-        <v>14</v>
-      </c>
-      <c r="I136" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A137" t="s">
-        <v>212</v>
-      </c>
-      <c r="B137" t="s">
-        <v>209</v>
-      </c>
-      <c r="C137" t="s">
-        <v>64</v>
-      </c>
-      <c r="D137" t="s">
-        <v>59</v>
-      </c>
-      <c r="E137" t="s">
-        <v>60</v>
-      </c>
-      <c r="F137" t="s">
-        <v>61</v>
-      </c>
-      <c r="G137" t="s">
-        <v>13</v>
-      </c>
-      <c r="H137" t="s">
-        <v>14</v>
-      </c>
-      <c r="I137" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A138" t="s">
-        <v>213</v>
-      </c>
-      <c r="B138" t="s">
-        <v>200</v>
-      </c>
-      <c r="C138" t="s">
-        <v>59</v>
-      </c>
-      <c r="D138" t="s">
-        <v>60</v>
-      </c>
-      <c r="E138" t="s">
-        <v>61</v>
-      </c>
-      <c r="F138" t="s">
-        <v>13</v>
-      </c>
-      <c r="G138" t="s">
-        <v>14</v>
-      </c>
-      <c r="H138" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A139" t="s">
-        <v>214</v>
-      </c>
-      <c r="B139" t="s">
-        <v>200</v>
-      </c>
-      <c r="C139" t="s">
-        <v>59</v>
-      </c>
-      <c r="D139" t="s">
-        <v>60</v>
-      </c>
-      <c r="E139" t="s">
-        <v>61</v>
-      </c>
-      <c r="F139" t="s">
-        <v>13</v>
-      </c>
-      <c r="G139" t="s">
-        <v>14</v>
-      </c>
-      <c r="H139" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A140" t="s">
-        <v>215</v>
-      </c>
-      <c r="B140" t="s">
-        <v>200</v>
-      </c>
-      <c r="C140" t="s">
-        <v>59</v>
-      </c>
-      <c r="D140" t="s">
-        <v>60</v>
-      </c>
-      <c r="E140" t="s">
-        <v>61</v>
-      </c>
-      <c r="F140" t="s">
-        <v>13</v>
-      </c>
-      <c r="G140" t="s">
-        <v>14</v>
-      </c>
-      <c r="H140" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A141" t="s">
-        <v>216</v>
-      </c>
-      <c r="B141" t="s">
-        <v>118</v>
-      </c>
-      <c r="C141" t="s">
-        <v>59</v>
-      </c>
-      <c r="D141" t="s">
-        <v>60</v>
-      </c>
-      <c r="E141" t="s">
-        <v>61</v>
-      </c>
-      <c r="F141" t="s">
-        <v>13</v>
-      </c>
-      <c r="G141" t="s">
-        <v>14</v>
-      </c>
-      <c r="H141" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A142" t="s">
-        <v>216</v>
-      </c>
-      <c r="B142" t="s">
-        <v>68</v>
-      </c>
-      <c r="C142" t="s">
+      <c r="C144" t="s">
+        <v>70</v>
+      </c>
+      <c r="D144" t="s">
+        <v>67</v>
+      </c>
+      <c r="E144" t="s">
+        <v>60</v>
+      </c>
+      <c r="F144" t="s">
+        <v>61</v>
+      </c>
+      <c r="G144" t="s">
+        <v>62</v>
+      </c>
+      <c r="H144" t="s">
+        <v>13</v>
+      </c>
+      <c r="I144" t="s">
+        <v>14</v>
+      </c>
+      <c r="J144" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10">
+      <c r="A145" t="s">
+        <v>219</v>
+      </c>
+      <c r="B145" t="s">
+        <v>120</v>
+      </c>
+      <c r="C145" t="s">
+        <v>60</v>
+      </c>
+      <c r="D145" t="s">
+        <v>61</v>
+      </c>
+      <c r="E145" t="s">
+        <v>62</v>
+      </c>
+      <c r="F145" t="s">
+        <v>13</v>
+      </c>
+      <c r="G145" t="s">
+        <v>14</v>
+      </c>
+      <c r="H145" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10">
+      <c r="A146" t="s">
+        <v>219</v>
+      </c>
+      <c r="B146" t="s">
         <v>69</v>
       </c>
-      <c r="D142" t="s">
-        <v>66</v>
-      </c>
-      <c r="E142" t="s">
-        <v>59</v>
-      </c>
-      <c r="F142" t="s">
-        <v>60</v>
-      </c>
-      <c r="G142" t="s">
-        <v>61</v>
-      </c>
-      <c r="H142" t="s">
-        <v>13</v>
-      </c>
-      <c r="I142" t="s">
-        <v>14</v>
-      </c>
-      <c r="J142" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A143" t="s">
-        <v>217</v>
-      </c>
-      <c r="B143" t="s">
-        <v>118</v>
-      </c>
-      <c r="C143" t="s">
-        <v>59</v>
-      </c>
-      <c r="D143" t="s">
-        <v>60</v>
-      </c>
-      <c r="E143" t="s">
-        <v>61</v>
-      </c>
-      <c r="F143" t="s">
-        <v>13</v>
-      </c>
-      <c r="G143" t="s">
-        <v>14</v>
-      </c>
-      <c r="H143" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A144" t="s">
-        <v>217</v>
-      </c>
-      <c r="B144" t="s">
-        <v>68</v>
-      </c>
-      <c r="C144" t="s">
+      <c r="C146" t="s">
+        <v>70</v>
+      </c>
+      <c r="D146" t="s">
+        <v>67</v>
+      </c>
+      <c r="E146" t="s">
+        <v>60</v>
+      </c>
+      <c r="F146" t="s">
+        <v>61</v>
+      </c>
+      <c r="G146" t="s">
+        <v>62</v>
+      </c>
+      <c r="H146" t="s">
+        <v>13</v>
+      </c>
+      <c r="I146" t="s">
+        <v>14</v>
+      </c>
+      <c r="J146" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10">
+      <c r="A147" t="s">
+        <v>220</v>
+      </c>
+      <c r="B147" t="s">
+        <v>120</v>
+      </c>
+      <c r="C147" t="s">
+        <v>60</v>
+      </c>
+      <c r="D147" t="s">
+        <v>61</v>
+      </c>
+      <c r="E147" t="s">
+        <v>62</v>
+      </c>
+      <c r="F147" t="s">
+        <v>13</v>
+      </c>
+      <c r="G147" t="s">
+        <v>14</v>
+      </c>
+      <c r="H147" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10">
+      <c r="A148" t="s">
+        <v>220</v>
+      </c>
+      <c r="B148" t="s">
         <v>69</v>
       </c>
-      <c r="D144" t="s">
-        <v>66</v>
-      </c>
-      <c r="E144" t="s">
-        <v>59</v>
-      </c>
-      <c r="F144" t="s">
-        <v>60</v>
-      </c>
-      <c r="G144" t="s">
-        <v>61</v>
-      </c>
-      <c r="H144" t="s">
-        <v>13</v>
-      </c>
-      <c r="I144" t="s">
-        <v>14</v>
-      </c>
-      <c r="J144" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A145" t="s">
-        <v>218</v>
-      </c>
-      <c r="B145" t="s">
-        <v>118</v>
-      </c>
-      <c r="C145" t="s">
-        <v>59</v>
-      </c>
-      <c r="D145" t="s">
-        <v>60</v>
-      </c>
-      <c r="E145" t="s">
-        <v>61</v>
-      </c>
-      <c r="F145" t="s">
-        <v>13</v>
-      </c>
-      <c r="G145" t="s">
-        <v>14</v>
-      </c>
-      <c r="H145" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A146" t="s">
-        <v>218</v>
-      </c>
-      <c r="B146" t="s">
-        <v>68</v>
-      </c>
-      <c r="C146" t="s">
-        <v>69</v>
-      </c>
-      <c r="D146" t="s">
-        <v>66</v>
-      </c>
-      <c r="E146" t="s">
-        <v>59</v>
-      </c>
-      <c r="F146" t="s">
-        <v>60</v>
-      </c>
-      <c r="G146" t="s">
-        <v>61</v>
-      </c>
-      <c r="H146" t="s">
-        <v>13</v>
-      </c>
-      <c r="I146" t="s">
-        <v>14</v>
-      </c>
-      <c r="J146" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A147" t="s">
-        <v>219</v>
-      </c>
-      <c r="B147" t="s">
-        <v>118</v>
-      </c>
-      <c r="C147" t="s">
-        <v>59</v>
-      </c>
-      <c r="D147" t="s">
-        <v>60</v>
-      </c>
-      <c r="E147" t="s">
-        <v>61</v>
-      </c>
-      <c r="F147" t="s">
-        <v>13</v>
-      </c>
-      <c r="G147" t="s">
-        <v>14</v>
-      </c>
-      <c r="H147" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A148" t="s">
-        <v>219</v>
-      </c>
-      <c r="B148" t="s">
-        <v>68</v>
-      </c>
       <c r="C148" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D148" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E148" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F148" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G148" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H148" t="s">
         <v>13</v>
@@ -5704,21 +5672,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="149" spans="1:10">
       <c r="A149" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B149" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C149" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D149" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E149" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F149" t="s">
         <v>13</v>
@@ -5730,15 +5698,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="150" spans="1:10">
       <c r="A150" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B150" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C150" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D150" t="s">
         <v>41</v>
@@ -5753,15 +5721,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="151" spans="1:10">
       <c r="A151" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B151" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C151" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D151" t="s">
         <v>41</v>
@@ -5776,12 +5744,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="152" spans="1:10">
       <c r="A152" t="s">
-        <v>226</v>
-      </c>
-      <c r="B152" s="3" t="s">
         <v>227</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>228</v>
       </c>
       <c r="C152" t="s">
         <v>45</v>
@@ -5799,24 +5767,24 @@
         <v>15</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="153" spans="1:10">
       <c r="A153" t="s">
-        <v>228</v>
-      </c>
-      <c r="B153" s="3" t="s">
         <v>229</v>
       </c>
+      <c r="B153" s="2" t="s">
+        <v>230</v>
+      </c>
       <c r="C153" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D153" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E153" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F153" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G153" t="s">
         <v>13</v>
@@ -5828,12 +5796,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="154" spans="1:10">
       <c r="A154" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B154" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C154" t="s">
         <v>45</v>
@@ -5851,24 +5819,24 @@
         <v>15</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="155" spans="1:10">
       <c r="A155" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B155" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C155" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D155" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E155" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F155" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G155" t="s">
         <v>13</v>
@@ -5880,24 +5848,24 @@
         <v>15</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="156" spans="1:10">
       <c r="A156" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B156" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C156" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D156" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E156" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F156" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G156" t="s">
         <v>13</v>
@@ -5909,24 +5877,24 @@
         <v>15</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="157" spans="1:10">
       <c r="A157" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B157" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C157" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D157" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E157" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F157" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G157" t="s">
         <v>13</v>
@@ -5938,12 +5906,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="158" spans="1:10">
       <c r="A158" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B158" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C158" t="s">
         <v>42</v>
@@ -5955,12 +5923,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="159" spans="1:10">
       <c r="A159" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B159" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C159" t="s">
         <v>12</v>
@@ -5975,15 +5943,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="160" spans="1:10">
       <c r="A160" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B160" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C160" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D160" t="s">
         <v>41</v>
@@ -5998,12 +5966,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="161" spans="1:9">
       <c r="A161" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B161" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C161" t="s">
         <v>45</v>
@@ -6021,76 +5989,76 @@
         <v>15</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="162" spans="1:9">
       <c r="A162" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B162" t="s">
+        <v>245</v>
+      </c>
+      <c r="C162" t="s">
+        <v>60</v>
+      </c>
+      <c r="D162" t="s">
+        <v>61</v>
+      </c>
+      <c r="E162" t="s">
+        <v>62</v>
+      </c>
+      <c r="F162" t="s">
+        <v>13</v>
+      </c>
+      <c r="G162" t="s">
+        <v>14</v>
+      </c>
+      <c r="H162" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9">
+      <c r="A163" t="s">
         <v>244</v>
       </c>
-      <c r="C162" t="s">
-        <v>59</v>
-      </c>
-      <c r="D162" t="s">
-        <v>60</v>
-      </c>
-      <c r="E162" t="s">
-        <v>61</v>
-      </c>
-      <c r="F162" t="s">
-        <v>13</v>
-      </c>
-      <c r="G162" t="s">
-        <v>14</v>
-      </c>
-      <c r="H162" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.65">
-      <c r="A163" t="s">
-        <v>243</v>
-      </c>
       <c r="B163" t="s">
+        <v>246</v>
+      </c>
+      <c r="C163" t="s">
+        <v>67</v>
+      </c>
+      <c r="D163" t="s">
+        <v>60</v>
+      </c>
+      <c r="E163" t="s">
+        <v>61</v>
+      </c>
+      <c r="F163" t="s">
+        <v>62</v>
+      </c>
+      <c r="G163" t="s">
+        <v>13</v>
+      </c>
+      <c r="H163" t="s">
+        <v>14</v>
+      </c>
+      <c r="I163" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9">
+      <c r="A164" t="s">
+        <v>247</v>
+      </c>
+      <c r="B164" t="s">
         <v>245</v>
       </c>
-      <c r="C163" t="s">
-        <v>66</v>
-      </c>
-      <c r="D163" t="s">
-        <v>59</v>
-      </c>
-      <c r="E163" t="s">
-        <v>60</v>
-      </c>
-      <c r="F163" t="s">
-        <v>61</v>
-      </c>
-      <c r="G163" t="s">
-        <v>13</v>
-      </c>
-      <c r="H163" t="s">
-        <v>14</v>
-      </c>
-      <c r="I163" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.65">
-      <c r="A164" t="s">
-        <v>246</v>
-      </c>
-      <c r="B164" t="s">
-        <v>244</v>
-      </c>
       <c r="C164" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D164" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E164" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F164" t="s">
         <v>13</v>
@@ -6102,21 +6070,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="165" spans="1:9">
       <c r="A165" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B165" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C165" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D165" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E165" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F165" t="s">
         <v>13</v>
@@ -6128,15 +6096,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="166" spans="1:9">
       <c r="A166" t="s">
-        <v>249</v>
-      </c>
-      <c r="B166" s="3" t="s">
         <v>250</v>
       </c>
+      <c r="B166" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="C166" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D166" t="s">
         <v>41</v>
@@ -6151,15 +6119,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="167" spans="1:9">
       <c r="A167" t="s">
+        <v>252</v>
+      </c>
+      <c r="B167" t="s">
         <v>251</v>
       </c>
-      <c r="B167" t="s">
-        <v>250</v>
-      </c>
       <c r="C167" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D167" t="s">
         <v>41</v>
@@ -6174,15 +6142,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="168" spans="1:9">
       <c r="A168" t="s">
-        <v>252</v>
-      </c>
-      <c r="B168" s="3" t="s">
         <v>253</v>
       </c>
+      <c r="B168" s="2" t="s">
+        <v>254</v>
+      </c>
       <c r="C168" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D168" t="s">
         <v>41</v>
@@ -6197,15 +6165,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="169" spans="1:9">
       <c r="A169" t="s">
-        <v>254</v>
-      </c>
-      <c r="B169" s="3" t="s">
         <v>255</v>
       </c>
+      <c r="B169" s="2" t="s">
+        <v>256</v>
+      </c>
       <c r="C169" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D169" t="s">
         <v>41</v>
@@ -6220,21 +6188,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="170" spans="1:9">
       <c r="A170" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B170" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C170" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D170" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E170" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F170" t="s">
         <v>13</v>
@@ -6246,21 +6214,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="171" spans="1:9">
       <c r="A171" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B171" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C171" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D171" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E171" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F171" t="s">
         <v>13</v>
@@ -6272,12 +6240,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="172" spans="1:9">
       <c r="A172" t="s">
-        <v>258</v>
-      </c>
-      <c r="B172" s="3" t="s">
         <v>259</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>260</v>
       </c>
       <c r="C172" t="s">
         <v>45</v>
@@ -6295,21 +6263,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="173" spans="1:9">
       <c r="A173" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B173" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C173" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D173" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E173" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F173" t="s">
         <v>13</v>
@@ -6321,21 +6289,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="174" spans="1:9">
       <c r="A174" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B174" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C174" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D174" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E174" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F174" t="s">
         <v>13</v>
@@ -6347,21 +6315,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="175" spans="1:9">
       <c r="A175" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B175" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C175" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D175" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E175" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F175" t="s">
         <v>13</v>
@@ -6373,21 +6341,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="176" spans="1:9">
       <c r="A176" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B176" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C176" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D176" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E176" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F176" t="s">
         <v>13</v>
@@ -6399,21 +6367,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="177" spans="1:9">
       <c r="A177" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B177" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C177" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D177" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E177" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F177" t="s">
         <v>13</v>
@@ -6425,12 +6393,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="178" spans="1:9">
       <c r="A178" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B178" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C178" t="s">
         <v>42</v>
@@ -6442,21 +6410,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="179" spans="1:9">
       <c r="A179" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B179" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C179" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D179" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E179" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F179" t="s">
         <v>13</v>
@@ -6468,15 +6436,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="180" spans="1:9">
       <c r="A180" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B180" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C180" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D180" t="s">
         <v>41</v>
@@ -6491,41 +6459,41 @@
         <v>15</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="181" spans="1:9">
       <c r="A181" t="s">
+        <v>270</v>
+      </c>
+      <c r="B181" t="s">
+        <v>249</v>
+      </c>
+      <c r="C181" t="s">
+        <v>60</v>
+      </c>
+      <c r="D181" t="s">
+        <v>61</v>
+      </c>
+      <c r="E181" t="s">
+        <v>62</v>
+      </c>
+      <c r="F181" t="s">
+        <v>13</v>
+      </c>
+      <c r="G181" t="s">
+        <v>14</v>
+      </c>
+      <c r="H181" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9">
+      <c r="A182" t="s">
+        <v>271</v>
+      </c>
+      <c r="B182" t="s">
         <v>269</v>
       </c>
-      <c r="B181" t="s">
-        <v>248</v>
-      </c>
-      <c r="C181" t="s">
-        <v>59</v>
-      </c>
-      <c r="D181" t="s">
-        <v>60</v>
-      </c>
-      <c r="E181" t="s">
-        <v>61</v>
-      </c>
-      <c r="F181" t="s">
-        <v>13</v>
-      </c>
-      <c r="G181" t="s">
-        <v>14</v>
-      </c>
-      <c r="H181" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.65">
-      <c r="A182" t="s">
-        <v>270</v>
-      </c>
-      <c r="B182" t="s">
-        <v>268</v>
-      </c>
       <c r="C182" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D182" t="s">
         <v>41</v>
@@ -6540,15 +6508,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="183" spans="1:9">
       <c r="A183" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B183" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C183" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D183" t="s">
         <v>41</v>
@@ -6563,12 +6531,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="184" spans="1:9">
       <c r="A184" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B184" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C184" t="s">
         <v>45</v>
@@ -6586,12 +6554,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="185" spans="1:9">
       <c r="A185" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B185" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C185" t="s">
         <v>42</v>
@@ -6603,24 +6571,24 @@
         <v>15</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="186" spans="1:9">
       <c r="A186" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B186" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C186" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D186" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E186" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F186" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G186" t="s">
         <v>13</v>
@@ -6632,12 +6600,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="187" spans="1:9">
       <c r="A187" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B187" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C187" t="s">
         <v>45</v>
@@ -6655,12 +6623,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="188" spans="1:9">
       <c r="A188" t="s">
+        <v>282</v>
+      </c>
+      <c r="B188" t="s">
         <v>281</v>
-      </c>
-      <c r="B188" t="s">
-        <v>280</v>
       </c>
       <c r="C188" t="s">
         <v>45</v>
@@ -6678,12 +6646,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="189" spans="1:9">
       <c r="A189" t="s">
-        <v>282</v>
-      </c>
-      <c r="B189" s="3" t="s">
         <v>283</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>284</v>
       </c>
       <c r="C189" t="s">
         <v>45</v>
@@ -6701,12 +6669,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="190" spans="1:9">
       <c r="A190" t="s">
-        <v>284</v>
-      </c>
-      <c r="B190" s="3" t="s">
         <v>285</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>286</v>
       </c>
       <c r="C190" t="s">
         <v>41</v>
@@ -6721,15 +6689,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="191" spans="1:9">
       <c r="A191" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B191" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C191" t="s">
-        <v>342</v>
+        <v>289</v>
       </c>
       <c r="D191" t="s">
         <v>12</v>
@@ -6744,43 +6712,43 @@
         <v>15</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.65">
+    <row r="192" spans="1:9">
       <c r="A192" t="s">
+        <v>290</v>
+      </c>
+      <c r="B192" t="s">
+        <v>73</v>
+      </c>
+      <c r="C192" t="s">
+        <v>14</v>
+      </c>
+      <c r="D192" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10">
+      <c r="A193" t="s">
+        <v>291</v>
+      </c>
+      <c r="B193" t="s">
+        <v>73</v>
+      </c>
+      <c r="C193" t="s">
+        <v>14</v>
+      </c>
+      <c r="D193" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10">
+      <c r="A194" t="s">
+        <v>292</v>
+      </c>
+      <c r="B194" t="s">
         <v>288</v>
       </c>
-      <c r="B192" t="s">
-        <v>341</v>
-      </c>
-      <c r="C192" t="s">
-        <v>14</v>
-      </c>
-      <c r="D192" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A193" t="s">
+      <c r="C194" t="s">
         <v>289</v>
-      </c>
-      <c r="B193" t="s">
-        <v>341</v>
-      </c>
-      <c r="C193" t="s">
-        <v>14</v>
-      </c>
-      <c r="D193" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A194" t="s">
-        <v>290</v>
-      </c>
-      <c r="B194" t="s">
-        <v>287</v>
-      </c>
-      <c r="C194" t="s">
-        <v>342</v>
       </c>
       <c r="D194" t="s">
         <v>12</v>
@@ -6795,15 +6763,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="195" spans="1:10">
       <c r="A195" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B195" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C195" t="s">
-        <v>342</v>
+        <v>289</v>
       </c>
       <c r="D195" t="s">
         <v>12</v>
@@ -6818,15 +6786,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="196" spans="1:10">
       <c r="A196" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B196" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C196" t="s">
-        <v>342</v>
+        <v>289</v>
       </c>
       <c r="D196" t="s">
         <v>12</v>
@@ -6841,27 +6809,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="197" spans="1:10">
       <c r="A197" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B197" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C197" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D197" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E197" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F197" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G197" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H197" t="s">
         <v>13</v>
@@ -6873,27 +6841,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="198" spans="1:10">
       <c r="A198" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B198" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C198" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D198" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E198" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F198" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G198" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H198" t="s">
         <v>13</v>
@@ -6905,27 +6873,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="199" spans="1:10">
       <c r="A199" t="s">
+        <v>298</v>
+      </c>
+      <c r="B199" t="s">
         <v>296</v>
       </c>
-      <c r="B199" t="s">
-        <v>294</v>
-      </c>
       <c r="C199" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D199" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E199" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F199" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G199" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H199" t="s">
         <v>13</v>
@@ -6937,27 +6905,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="200" spans="1:10">
       <c r="A200" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B200" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C200" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D200" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E200" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F200" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G200" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H200" t="s">
         <v>13</v>
@@ -6969,27 +6937,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="201" spans="1:10">
       <c r="A201" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B201" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C201" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D201" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E201" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F201" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G201" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H201" t="s">
         <v>13</v>
@@ -7001,24 +6969,24 @@
         <v>15</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="202" spans="1:10">
       <c r="A202" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B202" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C202" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D202" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E202" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F202" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G202" t="s">
         <v>13</v>
@@ -7030,24 +6998,24 @@
         <v>15</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="203" spans="1:10">
       <c r="A203" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B203" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C203" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D203" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E203" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F203" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G203" t="s">
         <v>13</v>
@@ -7059,24 +7027,24 @@
         <v>15</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="204" spans="1:10">
       <c r="A204" t="s">
+        <v>304</v>
+      </c>
+      <c r="B204" t="s">
         <v>302</v>
       </c>
-      <c r="B204" t="s">
-        <v>300</v>
-      </c>
       <c r="C204" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D204" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E204" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F204" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G204" t="s">
         <v>13</v>
@@ -7088,46 +7056,46 @@
         <v>15</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="205" spans="1:10">
       <c r="A205" t="s">
-        <v>303</v>
-      </c>
-      <c r="B205" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B205" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C205" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="206" spans="1:10">
       <c r="A206" t="s">
         <v>15</v>
       </c>
-      <c r="B206" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.65">
+      <c r="B206" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10">
       <c r="A207" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B207" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C207" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D207" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E207" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F207" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G207" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H207" t="s">
         <v>13</v>
@@ -7139,27 +7107,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="208" spans="1:10">
       <c r="A208" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B208" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C208" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D208" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E208" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F208" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G208" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H208" t="s">
         <v>13</v>
@@ -7171,15 +7139,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.65">
+    <row r="209" spans="1:7">
       <c r="A209" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B209" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C209" t="s">
-        <v>340</v>
+        <v>181</v>
       </c>
       <c r="D209" t="s">
         <v>12</v>
@@ -7194,12 +7162,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.65">
+    <row r="210" spans="1:7">
       <c r="A210" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B210" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="C210" t="s">
         <v>14</v>
@@ -7208,12 +7176,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.65">
+    <row r="211" spans="1:7">
       <c r="A211" t="s">
-        <v>308</v>
-      </c>
-      <c r="B211" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>311</v>
       </c>
       <c r="C211" t="s">
         <v>51</v>
@@ -7228,12 +7196,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.65">
+    <row r="212" spans="1:7">
       <c r="A212" t="s">
-        <v>310</v>
-      </c>
-      <c r="B212" s="3" t="s">
-        <v>273</v>
+        <v>312</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>274</v>
       </c>
       <c r="C212" t="s">
         <v>41</v>
@@ -7248,12 +7216,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.65">
+    <row r="213" spans="1:7">
       <c r="A213" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B213" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="C213" t="s">
         <v>14</v>
@@ -7262,12 +7230,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.65">
+    <row r="214" spans="1:7">
       <c r="A214" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B214" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="C214" t="s">
         <v>14</v>
@@ -7276,11 +7244,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.65">
-      <c r="A215" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="B215" s="3" t="s">
+    <row r="215" spans="1:7">
+      <c r="A215" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B215" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C215" t="s">
@@ -7290,11 +7258,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.65">
-      <c r="A216" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="B216" s="3" t="s">
+    <row r="216" spans="1:7">
+      <c r="A216" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B216" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C216" t="s">
@@ -7304,11 +7272,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.65">
+    <row r="217" spans="1:7">
       <c r="A217" t="s">
-        <v>314</v>
-      </c>
-      <c r="B217" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B217" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C217" t="s">
@@ -7318,11 +7286,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.65">
+    <row r="218" spans="1:7">
       <c r="A218" t="s">
-        <v>315</v>
-      </c>
-      <c r="B218" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B218" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C218" t="s">
@@ -7335,15 +7303,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.65">
+    <row r="219" spans="1:7">
       <c r="A219" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B219" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C219" t="s">
-        <v>342</v>
+        <v>289</v>
       </c>
       <c r="D219" t="s">
         <v>12</v>
@@ -7358,12 +7326,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.65">
+    <row r="220" spans="1:7">
       <c r="A220" t="s">
-        <v>317</v>
-      </c>
-      <c r="B220" s="3" t="s">
-        <v>340</v>
+        <v>320</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>181</v>
       </c>
       <c r="C220" t="s">
         <v>12</v>
@@ -7378,11 +7346,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.65">
+    <row r="221" spans="1:7">
       <c r="A221" t="s">
-        <v>318</v>
-      </c>
-      <c r="B221" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B221" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C221" t="s">
@@ -7398,11 +7366,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.65">
+    <row r="222" spans="1:7">
       <c r="A222" t="s">
-        <v>319</v>
-      </c>
-      <c r="B222" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B222" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C222" t="s">
@@ -7418,12 +7386,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.65">
+    <row r="223" spans="1:7">
       <c r="A223" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B223" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C223" t="s">
         <v>12</v>
@@ -7438,15 +7406,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.65">
+    <row r="224" spans="1:7">
       <c r="A224" t="s">
-        <v>321</v>
-      </c>
-      <c r="B224" s="3" t="s">
-        <v>179</v>
+        <v>324</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>180</v>
       </c>
       <c r="C224" t="s">
-        <v>180</v>
+        <v>325</v>
       </c>
       <c r="D224" t="s">
         <v>12</v>
@@ -7461,15 +7429,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="225" spans="1:10">
       <c r="A225" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B225" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C225" t="s">
-        <v>340</v>
+        <v>181</v>
       </c>
       <c r="D225" t="s">
         <v>12</v>
@@ -7484,15 +7452,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="226" spans="1:10">
       <c r="A226" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B226" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C226" t="s">
-        <v>339</v>
+        <v>181</v>
       </c>
       <c r="D226" t="s">
         <v>12</v>
@@ -7507,15 +7475,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="227" spans="1:10">
       <c r="A227" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B227" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C227" t="s">
-        <v>339</v>
+        <v>181</v>
       </c>
       <c r="D227" t="s">
         <v>12</v>
@@ -7530,15 +7498,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="228" spans="1:10">
       <c r="A228" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B228" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C228" t="s">
-        <v>339</v>
+        <v>181</v>
       </c>
       <c r="D228" t="s">
         <v>12</v>
@@ -7553,27 +7521,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="229" spans="1:10">
       <c r="A229" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B229" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C229" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D229" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E229" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F229" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G229" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H229" t="s">
         <v>13</v>
@@ -7585,27 +7553,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="230" spans="1:10">
       <c r="A230" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B230" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C230" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D230" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E230" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F230" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G230" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H230" t="s">
         <v>13</v>
@@ -7617,27 +7585,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="231" spans="1:10">
       <c r="A231" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B231" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C231" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D231" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E231" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F231" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G231" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H231" t="s">
         <v>13</v>
@@ -7649,27 +7617,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="232" spans="1:10">
       <c r="A232" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B232" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C232" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D232" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E232" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F232" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G232" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H232" t="s">
         <v>13</v>
@@ -7681,15 +7649,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="233" spans="1:10">
       <c r="A233" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B233" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C233" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D233" t="s">
         <v>41</v>
@@ -7704,15 +7672,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="234" spans="1:10">
       <c r="A234" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B234" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C234" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D234" t="s">
         <v>41</v>
@@ -7727,15 +7695,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="235" spans="1:10">
       <c r="A235" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B235" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C235" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D235" t="s">
         <v>41</v>
@@ -7750,15 +7718,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="236" spans="1:10">
       <c r="A236" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B236" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C236" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D236" t="s">
         <v>41</v>
@@ -7773,34 +7741,34 @@
         <v>15</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A237" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="B237" s="3" t="s">
+    <row r="237" spans="1:10">
+      <c r="A237" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B237" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C237" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.65">
-      <c r="A238" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="B238" s="3" t="s">
+    <row r="238" spans="1:10">
+      <c r="A238" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="B238" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C238" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="239" spans="1:10">
       <c r="A239" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B239" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="C239" t="s">
         <v>14</v>
@@ -7809,12 +7777,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.65">
+    <row r="240" spans="1:10">
       <c r="A240" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B240" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C240" t="s">
         <v>49</v>
@@ -7836,79 +7804,88 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F8A958-5FA3-4958-A2E6-DE03D25AEFF4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.65"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85" outlineLevelRow="4" outlineLevelCol="6"/>
+  <cols>
+    <col min="2" max="2" width="23.4336283185841" customWidth="1"/>
+    <col min="3" max="3" width="26.0884955752212" customWidth="1"/>
+    <col min="4" max="4" width="26.9557522123894" customWidth="1"/>
+    <col min="5" max="5" width="45.141592920354" customWidth="1"/>
+    <col min="6" max="6" width="26.4867256637168" customWidth="1"/>
+    <col min="7" max="7" width="34.5221238938053" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B1" t="s">
         <v>345</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>346</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>347</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>348</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.65">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>350</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>351</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>352</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>353</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>354</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
         <v>356</v>
       </c>
-      <c r="G2" t="s">
+      <c r="B3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.65">
-      <c r="A3" t="s">
+      <c r="B4" t="s">
         <v>359</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.65">
-      <c r="A4" t="s">
-        <v>361</v>
-      </c>
-      <c r="B4" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.65">
-      <c r="A5" t="s">
-        <v>363</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>